--- a/Aim2/Aim2_Data/aim2_timestamps_final.xlsx
+++ b/Aim2/Aim2_Data/aim2_timestamps_final.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://chla.sharepoint.com/sites/BiostatsCore/Staff Files/My Vu/Elena Tenenbaum Aim 2/Updated_2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eb255/Desktop/github/RISE/Aim2/Aim2_Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{69DE93BF-86AB-B240-AC14-9F3A5CEB7DB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01B90A16-03F0-2B4D-82E9-A7591FA9B944}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{863D1FB5-F92D-364A-BFA7-5CB1F6F7D9BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="440" yWindow="2000" windowWidth="28220" windowHeight="16180" activeTab="5" xr2:uid="{1905D5AD-B59A-4349-BC54-AD7B07C29ACC}"/>
+    <workbookView xWindow="440" yWindow="2000" windowWidth="28220" windowHeight="16180" activeTab="4" xr2:uid="{1905D5AD-B59A-4349-BC54-AD7B07C29ACC}"/>
   </bookViews>
   <sheets>
     <sheet name="GeoSocial" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1367" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1374" uniqueCount="287">
   <si>
     <t>Frame Start</t>
   </si>
@@ -900,6 +900,9 @@
   </si>
   <si>
     <t>blue left, yellow right</t>
+  </si>
+  <si>
+    <t>end_minus_start</t>
   </si>
 </sst>
 </file>
@@ -1325,7 +1328,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A723FD97-6B63-2843-8E5A-12061CB0C7C4}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="19.5" customWidth="1"/>
@@ -1335,7 +1338,7 @@
     <col min="6" max="6" width="15.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1354,8 +1357,11 @@
       <c r="F1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G1" s="4" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1376,8 +1382,12 @@
         <f>ROUND(D2*30,0)</f>
         <v>328</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G2">
+        <f>F2-E2</f>
+        <v>147</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1398,8 +1408,12 @@
         <f t="shared" ref="F3:F11" si="1">ROUND(D3*30,0)</f>
         <v>480</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G3">
+        <f>F3-E3</f>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1420,8 +1434,12 @@
         <f t="shared" si="1"/>
         <v>630</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G4">
+        <f>F4-E4</f>
+        <v>149</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1442,8 +1460,12 @@
         <f t="shared" si="1"/>
         <v>780</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G5">
+        <f>F5-E5</f>
+        <v>148</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1464,8 +1486,12 @@
         <f t="shared" si="1"/>
         <v>929</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G6">
+        <f>F6-E6</f>
+        <v>148</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1486,8 +1512,12 @@
         <f t="shared" si="1"/>
         <v>1082</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G7">
+        <f>F7-E7</f>
+        <v>152</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1508,8 +1538,12 @@
         <f t="shared" si="1"/>
         <v>1234</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G8">
+        <f>F8-E8</f>
+        <v>151</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1530,8 +1564,12 @@
         <f t="shared" si="1"/>
         <v>1383</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G9">
+        <f>F9-E9</f>
+        <v>148</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1552,8 +1590,12 @@
         <f t="shared" si="1"/>
         <v>1534</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G10">
+        <f>F10-E10</f>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1573,6 +1615,10 @@
       <c r="F11">
         <f t="shared" si="1"/>
         <v>1720</v>
+      </c>
+      <c r="G11">
+        <f>F11-E11</f>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -1582,14 +1628,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0569795-018A-454E-A86C-5367D9E0F514}">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.5" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="11.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1608,8 +1654,11 @@
       <c r="F1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G1" s="4" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1630,8 +1679,12 @@
         <f>LEFT(D2,2)*3600*30 + MID(D2,4,2)*60*30 + MID(D2,7,2)*30 + RIGHT(D2,2)</f>
         <v>586</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G2">
+        <f>F2-E2</f>
+        <v>399</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1652,8 +1705,12 @@
         <f t="shared" ref="F3:F7" si="1">LEFT(D3,2)*3600*30 + MID(D3,4,2)*60*30 + MID(D3,7,2)*30 + RIGHT(D3,2)</f>
         <v>1074</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G3">
+        <f t="shared" ref="G3:G7" si="2">F3-E3</f>
+        <v>398</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1674,8 +1731,12 @@
         <f t="shared" si="1"/>
         <v>1564</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G4">
+        <f t="shared" si="2"/>
+        <v>399</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1696,8 +1757,12 @@
         <f t="shared" si="1"/>
         <v>2055</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G5">
+        <f t="shared" si="2"/>
+        <v>399</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1718,8 +1783,12 @@
         <f t="shared" si="1"/>
         <v>2546</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G6">
+        <f t="shared" si="2"/>
+        <v>399</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1740,8 +1809,12 @@
         <f t="shared" si="1"/>
         <v>3038</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G7">
+        <f t="shared" si="2"/>
+        <v>399</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
     </row>
@@ -1752,7 +1825,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF2C760A-3F0F-9B4C-B32C-F0DB99EEF92D}">
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.5" bestFit="1" customWidth="1"/>
@@ -1761,7 +1834,7 @@
     <col min="7" max="7" width="14.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1792,8 +1865,11 @@
       <c r="J1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K1" s="4" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -1827,8 +1903,12 @@
         <f>H2+6</f>
         <v>75</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K2">
+        <f>J2-I2</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -1862,8 +1942,12 @@
         <f t="shared" ref="J3:J17" si="2">H3+6</f>
         <v>195</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K3">
+        <f t="shared" ref="K3:K17" si="3">J3-I3</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -1897,8 +1981,12 @@
         <f t="shared" si="2"/>
         <v>315</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K4">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -1932,8 +2020,12 @@
         <f t="shared" si="2"/>
         <v>435</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K5">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -1967,8 +2059,12 @@
         <f t="shared" si="2"/>
         <v>555</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K6">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -2002,8 +2098,12 @@
         <f t="shared" si="2"/>
         <v>675</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K7">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -2037,8 +2137,12 @@
         <f t="shared" si="2"/>
         <v>795</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K8">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -2072,8 +2176,12 @@
         <f t="shared" si="2"/>
         <v>915</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K9">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -2107,8 +2215,12 @@
         <f t="shared" si="2"/>
         <v>1035</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K10">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -2142,8 +2254,12 @@
         <f t="shared" si="2"/>
         <v>1155</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K11">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -2177,8 +2293,12 @@
         <f t="shared" si="2"/>
         <v>1275</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K12">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -2212,8 +2332,12 @@
         <f t="shared" si="2"/>
         <v>1395</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K13">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -2247,8 +2371,12 @@
         <f t="shared" si="2"/>
         <v>1515</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K14">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -2282,8 +2410,12 @@
         <f t="shared" si="2"/>
         <v>1635</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K15">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -2317,8 +2449,12 @@
         <f t="shared" si="2"/>
         <v>1755</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K16">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -2351,6 +2487,10 @@
       <c r="J17">
         <f t="shared" si="2"/>
         <v>1875</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="3"/>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -2360,7 +2500,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE25A399-0B6E-9F43-8135-606BE21B8DC7}">
-  <dimension ref="A1:M97"/>
+  <dimension ref="A1:M98"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.6640625" style="3" customWidth="1"/>
@@ -2403,7 +2543,9 @@
       <c r="H1" t="s">
         <v>1</v>
       </c>
-      <c r="I1"/>
+      <c r="I1" s="4" t="s">
+        <v>286</v>
+      </c>
       <c r="K1"/>
       <c r="M1"/>
     </row>
@@ -2434,7 +2576,10 @@
         <f>LEFT(F2,2)*3600*30 + MID(F2,4,2)*60*30 + MID(F2,7,2)*30 + RIGHT(F2,2)</f>
         <v>1397</v>
       </c>
-      <c r="I2" s="6"/>
+      <c r="I2">
+        <f>H2-G2</f>
+        <v>239</v>
+      </c>
       <c r="J2" s="4"/>
       <c r="K2" s="6"/>
       <c r="L2" s="4"/>
@@ -2467,7 +2612,10 @@
         <f t="shared" ref="H3:H32" si="1">LEFT(F3,2)*3600*30 + MID(F3,4,2)*60*30 + MID(F3,7,2)*30 + RIGHT(F3,2)</f>
         <v>1669</v>
       </c>
-      <c r="I3" s="6"/>
+      <c r="I3">
+        <f>H3-G3</f>
+        <v>239</v>
+      </c>
       <c r="J3" s="4"/>
       <c r="K3" s="6"/>
       <c r="L3" s="4"/>
@@ -2500,7 +2648,10 @@
         <f t="shared" si="1"/>
         <v>2843</v>
       </c>
-      <c r="I4" s="6"/>
+      <c r="I4">
+        <f>H4-G4</f>
+        <v>239</v>
+      </c>
       <c r="J4" s="4"/>
       <c r="K4" s="6"/>
       <c r="L4" s="4"/>
@@ -2533,7 +2684,10 @@
         <f t="shared" si="1"/>
         <v>3117</v>
       </c>
-      <c r="I5" s="6"/>
+      <c r="I5">
+        <f>H5-G5</f>
+        <v>239</v>
+      </c>
       <c r="J5" s="4"/>
       <c r="K5" s="6"/>
       <c r="L5" s="4"/>
@@ -2566,7 +2720,10 @@
         <f t="shared" si="1"/>
         <v>4285</v>
       </c>
-      <c r="I6" s="6"/>
+      <c r="I6">
+        <f>H6-G6</f>
+        <v>239</v>
+      </c>
       <c r="J6" s="4"/>
       <c r="K6" s="6"/>
       <c r="L6" s="4"/>
@@ -2599,7 +2756,10 @@
         <f t="shared" si="1"/>
         <v>4559</v>
       </c>
-      <c r="I7" s="6"/>
+      <c r="I7">
+        <f>H7-G7</f>
+        <v>239</v>
+      </c>
       <c r="J7" s="4"/>
       <c r="K7" s="6"/>
       <c r="L7" s="4"/>
@@ -2632,7 +2792,10 @@
         <f t="shared" si="1"/>
         <v>5703</v>
       </c>
-      <c r="I8" s="6"/>
+      <c r="I8">
+        <f>H8-G8</f>
+        <v>239</v>
+      </c>
       <c r="J8" s="4"/>
       <c r="K8" s="6"/>
       <c r="L8" s="4"/>
@@ -2665,7 +2828,10 @@
         <f t="shared" si="1"/>
         <v>6008</v>
       </c>
-      <c r="I9" s="6"/>
+      <c r="I9">
+        <f>H9-G9</f>
+        <v>240</v>
+      </c>
       <c r="J9" s="4"/>
       <c r="K9" s="6"/>
       <c r="L9" s="4"/>
@@ -2698,7 +2864,10 @@
         <f t="shared" si="1"/>
         <v>7145</v>
       </c>
-      <c r="I10" s="6"/>
+      <c r="I10">
+        <f>H10-G10</f>
+        <v>239</v>
+      </c>
       <c r="J10" s="4"/>
       <c r="K10" s="6"/>
       <c r="L10" s="4"/>
@@ -2731,7 +2900,10 @@
         <f t="shared" si="1"/>
         <v>7445</v>
       </c>
-      <c r="I11" s="6"/>
+      <c r="I11">
+        <f>H11-G11</f>
+        <v>239</v>
+      </c>
       <c r="J11" s="4"/>
       <c r="K11" s="6"/>
       <c r="L11" s="4"/>
@@ -2764,7 +2936,10 @@
         <f t="shared" si="1"/>
         <v>8585</v>
       </c>
-      <c r="I12" s="6"/>
+      <c r="I12">
+        <f>H12-G12</f>
+        <v>239</v>
+      </c>
       <c r="J12" s="4"/>
       <c r="K12" s="6"/>
       <c r="L12" s="4"/>
@@ -2797,7 +2972,10 @@
         <f t="shared" si="1"/>
         <v>8885</v>
       </c>
-      <c r="I13" s="7"/>
+      <c r="I13">
+        <f>H13-G13</f>
+        <v>239</v>
+      </c>
       <c r="K13" s="7"/>
       <c r="M13" s="7"/>
     </row>
@@ -2828,6 +3006,10 @@
         <f t="shared" si="1"/>
         <v>1397</v>
       </c>
+      <c r="I14">
+        <f>H14-G14</f>
+        <v>239</v>
+      </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
@@ -2856,6 +3038,10 @@
         <f t="shared" si="1"/>
         <v>1669</v>
       </c>
+      <c r="I15">
+        <f>H15-G15</f>
+        <v>239</v>
+      </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
@@ -2884,8 +3070,12 @@
         <f t="shared" si="1"/>
         <v>2845</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I16">
+        <f>H16-G16</f>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>216</v>
       </c>
@@ -2912,8 +3102,12 @@
         <f t="shared" si="1"/>
         <v>3117</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I17">
+        <f>H17-G17</f>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>217</v>
       </c>
@@ -2940,8 +3134,12 @@
         <f t="shared" si="1"/>
         <v>4263</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I18">
+        <f>H18-G18</f>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>218</v>
       </c>
@@ -2968,8 +3166,12 @@
         <f t="shared" si="1"/>
         <v>4567</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I19">
+        <f>H19-G19</f>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>219</v>
       </c>
@@ -2996,8 +3198,12 @@
         <f t="shared" si="1"/>
         <v>5715</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I20">
+        <f>H20-G20</f>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>220</v>
       </c>
@@ -3024,8 +3230,12 @@
         <f t="shared" si="1"/>
         <v>6019</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I21">
+        <f>H21-G21</f>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>221</v>
       </c>
@@ -3052,8 +3262,12 @@
         <f t="shared" si="1"/>
         <v>7165</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I22">
+        <f>H22-G22</f>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>222</v>
       </c>
@@ -3080,8 +3294,12 @@
         <f t="shared" si="1"/>
         <v>7469</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I23">
+        <f>H23-G23</f>
+        <v>269</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>223</v>
       </c>
@@ -3108,8 +3326,12 @@
         <f t="shared" si="1"/>
         <v>8613</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I24">
+        <f>H24-G24</f>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>224</v>
       </c>
@@ -3136,8 +3358,12 @@
         <f t="shared" si="1"/>
         <v>8887</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I25">
+        <f>H25-G25</f>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>213</v>
       </c>
@@ -3164,8 +3390,12 @@
         <f t="shared" si="1"/>
         <v>1391</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I26">
+        <f>H26-G26</f>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>214</v>
       </c>
@@ -3192,8 +3422,12 @@
         <f t="shared" si="1"/>
         <v>1663</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I27">
+        <f>H27-G27</f>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
         <v>215</v>
       </c>
@@ -3220,8 +3454,12 @@
         <f t="shared" si="1"/>
         <v>2837</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I28">
+        <f>H28-G28</f>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
         <v>216</v>
       </c>
@@ -3248,8 +3486,12 @@
         <f t="shared" si="1"/>
         <v>3111</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I29">
+        <f>H29-G29</f>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>217</v>
       </c>
@@ -3276,8 +3518,12 @@
         <f t="shared" si="1"/>
         <v>4283</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I30">
+        <f>H30-G30</f>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
         <v>218</v>
       </c>
@@ -3304,8 +3550,12 @@
         <f t="shared" si="1"/>
         <v>4555</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I31">
+        <f>H31-G31</f>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
         <v>219</v>
       </c>
@@ -3332,8 +3582,12 @@
         <f t="shared" si="1"/>
         <v>5727</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I32">
+        <f>H32-G32</f>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
         <v>220</v>
       </c>
@@ -3360,8 +3614,12 @@
         <f>LEFT(F33,2)*3600*30 + MID(F33,4,2)*60*30 + MID(F33,7,2)*30 + RIGHT(F33,2)</f>
         <v>6001</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I33">
+        <f t="shared" ref="I33:I96" si="2">H33-G33</f>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
         <v>221</v>
       </c>
@@ -3381,15 +3639,19 @@
         <v>115</v>
       </c>
       <c r="G34" s="6">
-        <f t="shared" ref="G34:G50" si="2">LEFT(E34,2)*3600*30 + MID(E34,4,2)*60*30 + MID(E34,7,2)*30 + RIGHT(E34,2)</f>
+        <f t="shared" ref="G34:G50" si="3">LEFT(E34,2)*3600*30 + MID(E34,4,2)*60*30 + MID(E34,7,2)*30 + RIGHT(E34,2)</f>
         <v>6904</v>
       </c>
       <c r="H34" s="6">
-        <f t="shared" ref="H34:H50" si="3">LEFT(F34,2)*3600*30 + MID(F34,4,2)*60*30 + MID(F34,7,2)*30 + RIGHT(F34,2)</f>
+        <f t="shared" ref="H34:H50" si="4">LEFT(F34,2)*3600*30 + MID(F34,4,2)*60*30 + MID(F34,7,2)*30 + RIGHT(F34,2)</f>
         <v>7143</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I34">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
         <v>222</v>
       </c>
@@ -3409,15 +3671,19 @@
         <v>52</v>
       </c>
       <c r="G35" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7206</v>
       </c>
       <c r="H35" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7445</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I35">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
         <v>223</v>
       </c>
@@ -3437,15 +3703,19 @@
         <v>54</v>
       </c>
       <c r="G36" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>8346</v>
       </c>
       <c r="H36" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8585</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I36">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
         <v>224</v>
       </c>
@@ -3465,15 +3735,19 @@
         <v>97</v>
       </c>
       <c r="G37" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>8648</v>
       </c>
       <c r="H37" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8887</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I37">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
         <v>213</v>
       </c>
@@ -3493,15 +3767,19 @@
         <v>117</v>
       </c>
       <c r="G38" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1162</v>
       </c>
       <c r="H38" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1401</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I38">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
         <v>214</v>
       </c>
@@ -3521,15 +3799,19 @@
         <v>119</v>
       </c>
       <c r="G39" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1434</v>
       </c>
       <c r="H39" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1673</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I39">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
         <v>215</v>
       </c>
@@ -3549,15 +3831,19 @@
         <v>121</v>
       </c>
       <c r="G40" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2608</v>
       </c>
       <c r="H40" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2847</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I40">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
         <v>216</v>
       </c>
@@ -3577,15 +3863,19 @@
         <v>123</v>
       </c>
       <c r="G41" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2880</v>
       </c>
       <c r="H41" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3119</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I41">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
         <v>217</v>
       </c>
@@ -3605,15 +3895,19 @@
         <v>125</v>
       </c>
       <c r="G42" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4022</v>
       </c>
       <c r="H42" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4261</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I42">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
         <v>218</v>
       </c>
@@ -3633,15 +3927,19 @@
         <v>127</v>
       </c>
       <c r="G43" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4326</v>
       </c>
       <c r="H43" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4565</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I43">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
         <v>219</v>
       </c>
@@ -3661,15 +3959,19 @@
         <v>87</v>
       </c>
       <c r="G44" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5476</v>
       </c>
       <c r="H44" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5715</v>
       </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I44">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
         <v>220</v>
       </c>
@@ -3689,15 +3991,19 @@
         <v>89</v>
       </c>
       <c r="G45" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5780</v>
       </c>
       <c r="H45" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6019</v>
       </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I45">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
         <v>221</v>
       </c>
@@ -3717,15 +4023,19 @@
         <v>91</v>
       </c>
       <c r="G46" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6926</v>
       </c>
       <c r="H46" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7165</v>
       </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I46">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
         <v>222</v>
       </c>
@@ -3745,15 +4055,19 @@
         <v>129</v>
       </c>
       <c r="G47" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7228</v>
       </c>
       <c r="H47" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7467</v>
       </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I47">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
         <v>223</v>
       </c>
@@ -3773,15 +4087,19 @@
         <v>95</v>
       </c>
       <c r="G48" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>8374</v>
       </c>
       <c r="H48" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8613</v>
       </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I48">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
         <v>224</v>
       </c>
@@ -3801,15 +4119,19 @@
         <v>97</v>
       </c>
       <c r="G49" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>8648</v>
       </c>
       <c r="H49" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8887</v>
       </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I49">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
         <v>213</v>
       </c>
@@ -3829,15 +4151,19 @@
         <v>131</v>
       </c>
       <c r="G50" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1156</v>
       </c>
       <c r="H50" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1395</v>
       </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I50">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
         <v>214</v>
       </c>
@@ -3864,8 +4190,12 @@
         <f>LEFT(F51,2)*3600*30 + MID(F51,4,2)*60*30 + MID(F51,7,2)*30 + RIGHT(F51,2)</f>
         <v>1667</v>
       </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I51">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
         <v>215</v>
       </c>
@@ -3885,15 +4215,19 @@
         <v>135</v>
       </c>
       <c r="G52" s="6">
-        <f t="shared" ref="G52:G71" si="4">LEFT(E52,2)*3600*30 + MID(E52,4,2)*60*30 + MID(E52,7,2)*30 + RIGHT(E52,2)</f>
+        <f t="shared" ref="G52:G71" si="5">LEFT(E52,2)*3600*30 + MID(E52,4,2)*60*30 + MID(E52,7,2)*30 + RIGHT(E52,2)</f>
         <v>2600</v>
       </c>
       <c r="H52" s="6">
-        <f t="shared" ref="H52:H71" si="5">LEFT(F52,2)*3600*30 + MID(F52,4,2)*60*30 + MID(F52,7,2)*30 + RIGHT(F52,2)</f>
+        <f t="shared" ref="H52:H71" si="6">LEFT(F52,2)*3600*30 + MID(F52,4,2)*60*30 + MID(F52,7,2)*30 + RIGHT(F52,2)</f>
         <v>2839</v>
       </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I52">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
         <v>216</v>
       </c>
@@ -3913,15 +4247,19 @@
         <v>105</v>
       </c>
       <c r="G53" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2872</v>
       </c>
       <c r="H53" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3111</v>
       </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I53">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
         <v>217</v>
       </c>
@@ -3941,15 +4279,19 @@
         <v>137</v>
       </c>
       <c r="G54" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4042</v>
       </c>
       <c r="H54" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4281</v>
       </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I54">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
         <v>218</v>
       </c>
@@ -3969,15 +4311,19 @@
         <v>139</v>
       </c>
       <c r="G55" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4314</v>
       </c>
       <c r="H55" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4553</v>
       </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I55">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
         <v>219</v>
       </c>
@@ -3997,15 +4343,19 @@
         <v>141</v>
       </c>
       <c r="G56" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5484</v>
       </c>
       <c r="H56" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>5723</v>
       </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I56">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" s="4" t="s">
         <v>220</v>
       </c>
@@ -4025,15 +4375,19 @@
         <v>143</v>
       </c>
       <c r="G57" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5754</v>
       </c>
       <c r="H57" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>5993</v>
       </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I57">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
         <v>221</v>
       </c>
@@ -4053,15 +4407,19 @@
         <v>145</v>
       </c>
       <c r="G58" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>6926</v>
       </c>
       <c r="H58" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>7165</v>
       </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I58">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" s="4" t="s">
         <v>222</v>
       </c>
@@ -4081,15 +4439,19 @@
         <v>147</v>
       </c>
       <c r="G59" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>7198</v>
       </c>
       <c r="H59" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>7437</v>
       </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I59">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
         <v>223</v>
       </c>
@@ -4109,15 +4471,19 @@
         <v>149</v>
       </c>
       <c r="G60" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>8368</v>
       </c>
       <c r="H60" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>8608</v>
       </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I60">
+        <f t="shared" si="2"/>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
         <v>224</v>
       </c>
@@ -4137,15 +4503,19 @@
         <v>151</v>
       </c>
       <c r="G61" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>8638</v>
       </c>
       <c r="H61" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>8877</v>
       </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I61">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
         <v>213</v>
       </c>
@@ -4165,15 +4535,19 @@
         <v>99</v>
       </c>
       <c r="G62" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1152</v>
       </c>
       <c r="H62" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1391</v>
       </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I62">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
         <v>214</v>
       </c>
@@ -4193,15 +4567,19 @@
         <v>101</v>
       </c>
       <c r="G63" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1424</v>
       </c>
       <c r="H63" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1663</v>
       </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I63">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
         <v>215</v>
       </c>
@@ -4221,15 +4599,19 @@
         <v>103</v>
       </c>
       <c r="G64" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2598</v>
       </c>
       <c r="H64" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2837</v>
       </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I64">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" s="4" t="s">
         <v>216</v>
       </c>
@@ -4249,15 +4631,19 @@
         <v>105</v>
       </c>
       <c r="G65" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2872</v>
       </c>
       <c r="H65" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3111</v>
       </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I65">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
         <v>217</v>
       </c>
@@ -4277,15 +4663,19 @@
         <v>107</v>
       </c>
       <c r="G66" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4044</v>
       </c>
       <c r="H66" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4283</v>
       </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I66">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" s="4" t="s">
         <v>218</v>
       </c>
@@ -4305,15 +4695,19 @@
         <v>109</v>
       </c>
       <c r="G67" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4316</v>
       </c>
       <c r="H67" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4555</v>
       </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I67">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" s="4" t="s">
         <v>219</v>
       </c>
@@ -4333,15 +4727,19 @@
         <v>153</v>
       </c>
       <c r="G68" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5460</v>
       </c>
       <c r="H68" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>5699</v>
       </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I68">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" s="4" t="s">
         <v>220</v>
       </c>
@@ -4361,15 +4759,19 @@
         <v>155</v>
       </c>
       <c r="G69" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5734</v>
       </c>
       <c r="H69" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>5973</v>
       </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I69">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" s="4" t="s">
         <v>221</v>
       </c>
@@ -4389,15 +4791,19 @@
         <v>157</v>
       </c>
       <c r="G70" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>6904</v>
       </c>
       <c r="H70" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>7143</v>
       </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I70">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" s="4" t="s">
         <v>222</v>
       </c>
@@ -4417,15 +4823,19 @@
         <v>159</v>
       </c>
       <c r="G71" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>7176</v>
       </c>
       <c r="H71" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>7415</v>
       </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I71">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" s="4" t="s">
         <v>223</v>
       </c>
@@ -4452,8 +4862,12 @@
         <f>LEFT(F72,2)*3600*30 + MID(F72,4,2)*60*30 + MID(F72,7,2)*30 + RIGHT(F72,2)</f>
         <v>8587</v>
       </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I72">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" s="4" t="s">
         <v>224</v>
       </c>
@@ -4473,15 +4887,19 @@
         <v>163</v>
       </c>
       <c r="G73" s="6">
-        <f t="shared" ref="G73:G84" si="6">LEFT(E73,2)*3600*30 + MID(E73,4,2)*60*30 + MID(E73,7,2)*30 + RIGHT(E73,2)</f>
+        <f t="shared" ref="G73:G84" si="7">LEFT(E73,2)*3600*30 + MID(E73,4,2)*60*30 + MID(E73,7,2)*30 + RIGHT(E73,2)</f>
         <v>8620</v>
       </c>
       <c r="H73" s="6">
-        <f t="shared" ref="H73:H84" si="7">LEFT(F73,2)*3600*30 + MID(F73,4,2)*60*30 + MID(F73,7,2)*30 + RIGHT(F73,2)</f>
+        <f t="shared" ref="H73:H84" si="8">LEFT(F73,2)*3600*30 + MID(F73,4,2)*60*30 + MID(F73,7,2)*30 + RIGHT(F73,2)</f>
         <v>8859</v>
       </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I73">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" s="4" t="s">
         <v>213</v>
       </c>
@@ -4501,15 +4919,19 @@
         <v>165</v>
       </c>
       <c r="G74" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1160</v>
       </c>
       <c r="H74" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1399</v>
       </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I74">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" s="4" t="s">
         <v>214</v>
       </c>
@@ -4529,15 +4951,19 @@
         <v>167</v>
       </c>
       <c r="G75" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1432</v>
       </c>
       <c r="H75" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1671</v>
       </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I75">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" s="4" t="s">
         <v>215</v>
       </c>
@@ -4557,15 +4983,19 @@
         <v>38</v>
       </c>
       <c r="G76" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2604</v>
       </c>
       <c r="H76" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2843</v>
       </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I76">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" s="4" t="s">
         <v>216</v>
       </c>
@@ -4585,15 +5015,19 @@
         <v>169</v>
       </c>
       <c r="G77" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2876</v>
       </c>
       <c r="H77" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3115</v>
       </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I77">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" s="4" t="s">
         <v>217</v>
       </c>
@@ -4613,15 +5047,19 @@
         <v>83</v>
       </c>
       <c r="G78" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4024</v>
       </c>
       <c r="H78" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4263</v>
       </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I78">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" s="4" t="s">
         <v>218</v>
       </c>
@@ -4641,15 +5079,19 @@
         <v>127</v>
       </c>
       <c r="G79" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4326</v>
       </c>
       <c r="H79" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4565</v>
       </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I79">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" s="4" t="s">
         <v>219</v>
       </c>
@@ -4669,15 +5111,19 @@
         <v>171</v>
       </c>
       <c r="G80" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>5468</v>
       </c>
       <c r="H80" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5707</v>
       </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I80">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" s="4" t="s">
         <v>220</v>
       </c>
@@ -4697,15 +5143,19 @@
         <v>173</v>
       </c>
       <c r="G81" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>5770</v>
       </c>
       <c r="H81" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>6009</v>
       </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I81">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82" s="4" t="s">
         <v>221</v>
       </c>
@@ -4725,15 +5175,19 @@
         <v>175</v>
       </c>
       <c r="G82" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>6914</v>
       </c>
       <c r="H82" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>7153</v>
       </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I82">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83" s="4" t="s">
         <v>222</v>
       </c>
@@ -4753,15 +5207,19 @@
         <v>177</v>
       </c>
       <c r="G83" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>7216</v>
       </c>
       <c r="H83" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>7455</v>
       </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I83">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84" s="4" t="s">
         <v>223</v>
       </c>
@@ -4781,15 +5239,19 @@
         <v>179</v>
       </c>
       <c r="G84" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>8356</v>
       </c>
       <c r="H84" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>8595</v>
       </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I84">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85" s="4" t="s">
         <v>224</v>
       </c>
@@ -4816,8 +5278,12 @@
         <f>LEFT(F85,2)*3600*30 + MID(F85,4,2)*60*30 + MID(F85,7,2)*30 + RIGHT(F85,2)</f>
         <v>8897</v>
       </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I85">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A86" s="4" t="s">
         <v>213</v>
       </c>
@@ -4837,15 +5303,19 @@
         <v>34</v>
       </c>
       <c r="G86" s="6">
-        <f t="shared" ref="G86:G97" si="8">LEFT(E86,2)*3600*30 + MID(E86,4,2)*60*30 + MID(E86,7,2)*30 + RIGHT(E86,2)</f>
+        <f t="shared" ref="G86:G97" si="9">LEFT(E86,2)*3600*30 + MID(E86,4,2)*60*30 + MID(E86,7,2)*30 + RIGHT(E86,2)</f>
         <v>1158</v>
       </c>
       <c r="H86" s="6">
-        <f t="shared" ref="H86:H97" si="9">LEFT(F86,2)*3600*30 + MID(F86,4,2)*60*30 + MID(F86,7,2)*30 + RIGHT(F86,2)</f>
+        <f t="shared" ref="H86:H97" si="10">LEFT(F86,2)*3600*30 + MID(F86,4,2)*60*30 + MID(F86,7,2)*30 + RIGHT(F86,2)</f>
         <v>1397</v>
       </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I86">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A87" s="4" t="s">
         <v>214</v>
       </c>
@@ -4865,15 +5335,19 @@
         <v>36</v>
       </c>
       <c r="G87" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1430</v>
       </c>
       <c r="H87" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1669</v>
       </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I87">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A88" s="4" t="s">
         <v>215</v>
       </c>
@@ -4893,15 +5367,19 @@
         <v>183</v>
       </c>
       <c r="G88" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2580</v>
       </c>
       <c r="H88" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2849</v>
       </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I88">
+        <f t="shared" si="2"/>
+        <v>269</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A89" s="4" t="s">
         <v>216</v>
       </c>
@@ -4921,15 +5399,19 @@
         <v>185</v>
       </c>
       <c r="G89" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2882</v>
       </c>
       <c r="H89" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3121</v>
       </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I89">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A90" s="4" t="s">
         <v>217</v>
       </c>
@@ -4949,15 +5431,19 @@
         <v>187</v>
       </c>
       <c r="G90" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4030</v>
       </c>
       <c r="H90" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>4269</v>
       </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I90">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A91" s="4" t="s">
         <v>218</v>
       </c>
@@ -4977,15 +5463,19 @@
         <v>189</v>
       </c>
       <c r="G91" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4332</v>
       </c>
       <c r="H91" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>4571</v>
       </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I91">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A92" s="4" t="s">
         <v>219</v>
       </c>
@@ -5005,15 +5495,19 @@
         <v>191</v>
       </c>
       <c r="G92" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>5480</v>
       </c>
       <c r="H92" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5719</v>
       </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I92">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93" s="4" t="s">
         <v>220</v>
       </c>
@@ -5033,15 +5527,19 @@
         <v>193</v>
       </c>
       <c r="G93" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>5782</v>
       </c>
       <c r="H93" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>6021</v>
       </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I93">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A94" s="4" t="s">
         <v>221</v>
       </c>
@@ -5061,15 +5559,19 @@
         <v>195</v>
       </c>
       <c r="G94" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>6924</v>
       </c>
       <c r="H94" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>7163</v>
       </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I94">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A95" s="4" t="s">
         <v>222</v>
       </c>
@@ -5089,15 +5591,19 @@
         <v>197</v>
       </c>
       <c r="G95" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>7226</v>
       </c>
       <c r="H95" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>7465</v>
       </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I95">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A96" s="4" t="s">
         <v>223</v>
       </c>
@@ -5117,15 +5623,19 @@
         <v>199</v>
       </c>
       <c r="G96" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>8366</v>
       </c>
       <c r="H96" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>8605</v>
       </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I96">
+        <f t="shared" si="2"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A97" s="4" t="s">
         <v>224</v>
       </c>
@@ -5145,13 +5655,20 @@
         <v>201</v>
       </c>
       <c r="G97" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>8668</v>
       </c>
       <c r="H97" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>8907</v>
       </c>
+      <c r="I97">
+        <f t="shared" ref="I97" si="11">H97-G97</f>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I98"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5160,14 +5677,14 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{406840D2-2351-0442-B27E-76241ED21B09}">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="18.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -5183,8 +5700,11 @@
       <c r="E1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F1" s="4" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5200,8 +5720,12 @@
       <c r="E2" s="1">
         <v>310</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F2">
+        <f>E2-D2</f>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -5217,8 +5741,12 @@
       <c r="E3" s="1">
         <v>520</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F3">
+        <f t="shared" ref="F3:F21" si="0">E3-D3</f>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -5234,8 +5762,12 @@
       <c r="E4" s="1">
         <v>730</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F4">
+        <f t="shared" si="0"/>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -5251,8 +5783,12 @@
       <c r="E5" s="1">
         <v>940</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F5">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -5268,8 +5804,12 @@
       <c r="E6" s="1">
         <v>1150</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -5285,8 +5825,12 @@
       <c r="E7" s="1">
         <v>1360</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -5302,8 +5846,12 @@
       <c r="E8" s="1">
         <v>1570</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F8">
+        <f t="shared" si="0"/>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -5319,8 +5867,12 @@
       <c r="E9" s="1">
         <v>1780</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F9">
+        <f t="shared" si="0"/>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -5336,8 +5888,12 @@
       <c r="E10" s="1">
         <v>1990</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F10">
+        <f t="shared" si="0"/>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -5353,8 +5909,12 @@
       <c r="E11" s="1">
         <v>2201</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F11">
+        <f t="shared" si="0"/>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12">
         <f>A11+1</f>
         <v>11</v>
@@ -5371,10 +5931,14 @@
       <c r="E12" s="1">
         <v>2412</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F12">
+        <f t="shared" si="0"/>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13">
-        <f t="shared" ref="A13:A21" si="0">A12+1</f>
+        <f t="shared" ref="A13:A21" si="1">A12+1</f>
         <v>12</v>
       </c>
       <c r="B13" t="s">
@@ -5389,10 +5953,14 @@
       <c r="E13" s="1">
         <v>2622</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F13">
+        <f t="shared" si="0"/>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="B14" t="s">
@@ -5407,10 +5975,14 @@
       <c r="E14" s="1">
         <v>2832</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F14">
+        <f t="shared" si="0"/>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="B15" t="s">
@@ -5425,10 +5997,14 @@
       <c r="E15" s="1">
         <v>3042</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F15">
+        <f t="shared" si="0"/>
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="B16" t="s">
@@ -5443,10 +6019,14 @@
       <c r="E16" s="1">
         <v>3252</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F16">
+        <f t="shared" si="0"/>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="B17" t="s">
@@ -5461,10 +6041,14 @@
       <c r="E17" s="1">
         <v>3460</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F17">
+        <f t="shared" si="0"/>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="B18" t="s">
@@ -5479,10 +6063,14 @@
       <c r="E18" s="1">
         <v>3670</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F18">
+        <f t="shared" si="0"/>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="B19" t="s">
@@ -5497,10 +6085,14 @@
       <c r="E19" s="1">
         <v>3880</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F19">
+        <f t="shared" si="0"/>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="B20" t="s">
@@ -5515,10 +6107,14 @@
       <c r="E20" s="1">
         <v>4090</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F20">
+        <f t="shared" si="0"/>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="B21" t="s">
@@ -5532,6 +6128,10 @@
       </c>
       <c r="E21" s="1">
         <v>4300</v>
+      </c>
+      <c r="F21">
+        <f t="shared" si="0"/>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -5541,7 +6141,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D2BF0A5-A8EE-604E-9491-0D3375FD8BBF}">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
@@ -5553,7 +6153,7 @@
     <col min="7" max="7" width="17.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>2</v>
       </c>
@@ -5578,8 +6178,11 @@
       <c r="H1" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I1" s="4" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="8">
         <v>1</v>
       </c>
@@ -5604,8 +6207,12 @@
       <c r="H2" s="8">
         <v>815</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I2">
+        <f>H2-G2</f>
+        <v>633</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="8">
         <v>2</v>
       </c>
@@ -5630,8 +6237,12 @@
       <c r="H3" s="8">
         <v>1601</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I3">
+        <f>H3-G3</f>
+        <v>603</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="8">
         <v>3</v>
       </c>
@@ -5656,8 +6267,12 @@
       <c r="H4" s="8">
         <v>2417</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I4">
+        <f>H4-G4</f>
+        <v>539</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="8">
         <v>4</v>
       </c>
@@ -5682,8 +6297,12 @@
       <c r="H5" s="8">
         <v>3183</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I5">
+        <f>H5-G5</f>
+        <v>563</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="8">
         <v>1</v>
       </c>
@@ -5708,8 +6327,12 @@
       <c r="H6" s="8">
         <v>815</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I6">
+        <f>H6-G6</f>
+        <v>633</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="8">
         <v>2</v>
       </c>
@@ -5734,8 +6357,12 @@
       <c r="H7" s="8">
         <v>1601</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I7">
+        <f>H7-G7</f>
+        <v>603</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="8">
         <v>3</v>
       </c>
@@ -5760,8 +6387,12 @@
       <c r="H8" s="8">
         <v>2417</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I8">
+        <f>H8-G8</f>
+        <v>539</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="8">
         <v>4</v>
       </c>
@@ -5786,8 +6417,12 @@
       <c r="H9" s="8">
         <v>3183</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I9">
+        <f>H9-G9</f>
+        <v>563</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="8">
         <v>1</v>
       </c>
@@ -5812,8 +6447,12 @@
       <c r="H10" s="8">
         <v>815</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I10">
+        <f>H10-G10</f>
+        <v>633</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="8">
         <v>2</v>
       </c>
@@ -5838,8 +6477,12 @@
       <c r="H11" s="8">
         <v>1601</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I11">
+        <f>H11-G11</f>
+        <v>603</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="8">
         <v>3</v>
       </c>
@@ -5864,8 +6507,12 @@
       <c r="H12" s="8">
         <v>2417</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I12">
+        <f>H12-G12</f>
+        <v>539</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="8">
         <v>4</v>
       </c>
@@ -5890,8 +6537,12 @@
       <c r="H13" s="8">
         <v>3183</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I13">
+        <f>H13-G13</f>
+        <v>563</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="8">
         <v>1</v>
       </c>
@@ -5916,8 +6567,12 @@
       <c r="H14" s="8">
         <v>815</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I14">
+        <f>H14-G14</f>
+        <v>633</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="8">
         <v>2</v>
       </c>
@@ -5942,8 +6597,12 @@
       <c r="H15" s="8">
         <v>1601</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I15">
+        <f>H15-G15</f>
+        <v>603</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="8">
         <v>3</v>
       </c>
@@ -5968,8 +6627,12 @@
       <c r="H16" s="8">
         <v>2417</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I16">
+        <f>H16-G16</f>
+        <v>539</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="8">
         <v>4</v>
       </c>
@@ -5993,6 +6656,10 @@
       </c>
       <c r="H17" s="8">
         <v>3183</v>
+      </c>
+      <c r="I17">
+        <f>H17-G17</f>
+        <v>563</v>
       </c>
     </row>
   </sheetData>
@@ -6002,7 +6669,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{439C113F-202D-B04C-996D-E55AD1706AE8}">
-  <dimension ref="A1:H114"/>
+  <dimension ref="A1:I114"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
@@ -6013,7 +6680,7 @@
     <col min="7" max="8" width="14.6640625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>2</v>
       </c>
@@ -6038,8 +6705,11 @@
       <c r="H1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I1" s="4" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="8">
         <v>1</v>
       </c>
@@ -6066,8 +6736,12 @@
         <f>LEFT(E2,2)*3600*30 + MID(E2,4,2)*60*30 + MID(E2,7,2)*30 + RIGHT(E2,2)</f>
         <v>846</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I2">
+        <f>H2-G2</f>
+        <v>660</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="8">
         <v>2</v>
       </c>
@@ -6094,8 +6768,12 @@
         <f t="shared" si="0"/>
         <v>1560</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I3">
+        <f t="shared" ref="I3:I66" si="1">H3-G3</f>
+        <v>654</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="8">
         <v>3</v>
       </c>
@@ -6122,8 +6800,12 @@
         <f t="shared" si="0"/>
         <v>2273</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I4">
+        <f t="shared" si="1"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="8">
         <v>4</v>
       </c>
@@ -6150,8 +6832,12 @@
         <f t="shared" si="0"/>
         <v>2986</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I5">
+        <f t="shared" si="1"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="8">
         <v>5</v>
       </c>
@@ -6178,8 +6864,12 @@
         <f t="shared" si="0"/>
         <v>3700</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I6">
+        <f t="shared" si="1"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="8">
         <v>6</v>
       </c>
@@ -6206,8 +6896,12 @@
         <f t="shared" si="0"/>
         <v>4413</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I7">
+        <f t="shared" si="1"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="8">
         <v>7</v>
       </c>
@@ -6234,8 +6928,12 @@
         <f t="shared" si="0"/>
         <v>5373</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I8">
+        <f t="shared" si="1"/>
+        <v>900</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="8">
         <v>8</v>
       </c>
@@ -6262,8 +6960,12 @@
         <f t="shared" si="0"/>
         <v>6117</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I9">
+        <f t="shared" si="1"/>
+        <v>684</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="8">
         <v>9</v>
       </c>
@@ -6290,8 +6992,12 @@
         <f t="shared" si="0"/>
         <v>6830</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I10">
+        <f t="shared" si="1"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="8">
         <v>10</v>
       </c>
@@ -6318,8 +7024,12 @@
         <f t="shared" si="0"/>
         <v>7543</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I11">
+        <f t="shared" si="1"/>
+        <v>654</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="8">
         <v>11</v>
       </c>
@@ -6346,8 +7056,12 @@
         <f t="shared" si="0"/>
         <v>8256</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I12">
+        <f t="shared" si="1"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="8">
         <v>12</v>
       </c>
@@ -6374,8 +7088,12 @@
         <f t="shared" si="0"/>
         <v>8969</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I13">
+        <f t="shared" si="1"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="8">
         <v>13</v>
       </c>
@@ -6402,8 +7120,12 @@
         <f t="shared" si="0"/>
         <v>9683</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I14">
+        <f t="shared" si="1"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="8">
         <v>14</v>
       </c>
@@ -6430,8 +7152,12 @@
         <f t="shared" si="0"/>
         <v>10642</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I15">
+        <f t="shared" si="1"/>
+        <v>899</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="8">
         <v>1</v>
       </c>
@@ -6458,8 +7184,12 @@
         <f t="shared" si="0"/>
         <v>846</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I16">
+        <f t="shared" si="1"/>
+        <v>660</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="8">
         <v>2</v>
       </c>
@@ -6486,8 +7216,12 @@
         <f t="shared" si="0"/>
         <v>1560</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I17">
+        <f t="shared" si="1"/>
+        <v>654</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="8">
         <v>3</v>
       </c>
@@ -6514,8 +7248,12 @@
         <f t="shared" si="0"/>
         <v>2273</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I18">
+        <f t="shared" si="1"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="8">
         <v>4</v>
       </c>
@@ -6542,8 +7280,12 @@
         <f t="shared" si="0"/>
         <v>2986</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I19">
+        <f t="shared" si="1"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="8">
         <v>5</v>
       </c>
@@ -6570,8 +7312,12 @@
         <f t="shared" si="0"/>
         <v>3700</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I20">
+        <f t="shared" si="1"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="8">
         <v>6</v>
       </c>
@@ -6598,8 +7344,12 @@
         <f t="shared" si="0"/>
         <v>4413</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I21">
+        <f t="shared" si="1"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="8">
         <v>7</v>
       </c>
@@ -6626,8 +7376,12 @@
         <f t="shared" si="0"/>
         <v>5373</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I22">
+        <f t="shared" si="1"/>
+        <v>900</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="8">
         <v>8</v>
       </c>
@@ -6654,8 +7408,12 @@
         <f t="shared" si="0"/>
         <v>6117</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I23">
+        <f t="shared" si="1"/>
+        <v>684</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="8">
         <v>9</v>
       </c>
@@ -6682,8 +7440,12 @@
         <f t="shared" si="0"/>
         <v>6830</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I24">
+        <f t="shared" si="1"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="8">
         <v>10</v>
       </c>
@@ -6710,8 +7472,12 @@
         <f t="shared" si="0"/>
         <v>7543</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I25">
+        <f t="shared" si="1"/>
+        <v>654</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="8">
         <v>11</v>
       </c>
@@ -6738,8 +7504,12 @@
         <f t="shared" si="0"/>
         <v>8256</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I26">
+        <f t="shared" si="1"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="8">
         <v>12</v>
       </c>
@@ -6766,8 +7536,12 @@
         <f t="shared" si="0"/>
         <v>8969</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I27">
+        <f t="shared" si="1"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="8">
         <v>13</v>
       </c>
@@ -6794,8 +7568,12 @@
         <f t="shared" si="0"/>
         <v>9683</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I28">
+        <f t="shared" si="1"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="8">
         <v>14</v>
       </c>
@@ -6822,8 +7600,12 @@
         <f t="shared" si="0"/>
         <v>10642</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I29">
+        <f t="shared" si="1"/>
+        <v>899</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="8">
         <v>1</v>
       </c>
@@ -6850,8 +7632,12 @@
         <f t="shared" si="0"/>
         <v>846</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I30">
+        <f t="shared" si="1"/>
+        <v>660</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="8">
         <v>2</v>
       </c>
@@ -6878,8 +7664,12 @@
         <f t="shared" si="0"/>
         <v>1560</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I31">
+        <f t="shared" si="1"/>
+        <v>654</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="8">
         <v>3</v>
       </c>
@@ -6906,8 +7696,12 @@
         <f t="shared" si="0"/>
         <v>2273</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I32">
+        <f t="shared" si="1"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="8">
         <v>4</v>
       </c>
@@ -6934,8 +7728,12 @@
         <f t="shared" si="0"/>
         <v>2986</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I33">
+        <f t="shared" si="1"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="8">
         <v>5</v>
       </c>
@@ -6962,8 +7760,12 @@
         <f t="shared" si="0"/>
         <v>3700</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I34">
+        <f t="shared" si="1"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="8">
         <v>6</v>
       </c>
@@ -6990,8 +7792,12 @@
         <f t="shared" si="0"/>
         <v>4413</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I35">
+        <f t="shared" si="1"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="8">
         <v>7</v>
       </c>
@@ -7018,8 +7824,12 @@
         <f t="shared" si="0"/>
         <v>5373</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I36">
+        <f t="shared" si="1"/>
+        <v>900</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="8">
         <v>8</v>
       </c>
@@ -7046,8 +7856,12 @@
         <f t="shared" si="0"/>
         <v>6117</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I37">
+        <f t="shared" si="1"/>
+        <v>684</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="8">
         <v>9</v>
       </c>
@@ -7074,8 +7888,12 @@
         <f t="shared" si="0"/>
         <v>6830</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I38">
+        <f t="shared" si="1"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" s="8">
         <v>10</v>
       </c>
@@ -7102,8 +7920,12 @@
         <f t="shared" si="0"/>
         <v>7543</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I39">
+        <f t="shared" si="1"/>
+        <v>654</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="8">
         <v>11</v>
       </c>
@@ -7130,8 +7952,12 @@
         <f t="shared" si="0"/>
         <v>8256</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I40">
+        <f t="shared" si="1"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" s="8">
         <v>12</v>
       </c>
@@ -7158,8 +7984,12 @@
         <f t="shared" si="0"/>
         <v>8969</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I41">
+        <f t="shared" si="1"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" s="8">
         <v>13</v>
       </c>
@@ -7186,8 +8016,12 @@
         <f t="shared" si="0"/>
         <v>9683</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I42">
+        <f t="shared" si="1"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" s="8">
         <v>14</v>
       </c>
@@ -7214,8 +8048,12 @@
         <f t="shared" si="0"/>
         <v>10642</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I43">
+        <f t="shared" si="1"/>
+        <v>899</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" s="8">
         <v>1</v>
       </c>
@@ -7242,8 +8080,12 @@
         <f t="shared" si="0"/>
         <v>846</v>
       </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I44">
+        <f t="shared" si="1"/>
+        <v>660</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" s="8">
         <v>2</v>
       </c>
@@ -7270,8 +8112,12 @@
         <f t="shared" si="0"/>
         <v>1560</v>
       </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I45">
+        <f t="shared" si="1"/>
+        <v>654</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" s="8">
         <v>3</v>
       </c>
@@ -7298,8 +8144,12 @@
         <f t="shared" si="0"/>
         <v>2273</v>
       </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I46">
+        <f t="shared" si="1"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" s="8">
         <v>4</v>
       </c>
@@ -7326,8 +8176,12 @@
         <f t="shared" si="0"/>
         <v>2986</v>
       </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I47">
+        <f t="shared" si="1"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" s="8">
         <v>5</v>
       </c>
@@ -7354,8 +8208,12 @@
         <f t="shared" si="0"/>
         <v>3700</v>
       </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I48">
+        <f t="shared" si="1"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" s="8">
         <v>6</v>
       </c>
@@ -7382,8 +8240,12 @@
         <f t="shared" si="0"/>
         <v>4413</v>
       </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I49">
+        <f t="shared" si="1"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" s="8">
         <v>7</v>
       </c>
@@ -7410,8 +8272,12 @@
         <f t="shared" si="0"/>
         <v>5373</v>
       </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I50">
+        <f t="shared" si="1"/>
+        <v>900</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" s="8">
         <v>8</v>
       </c>
@@ -7438,8 +8304,12 @@
         <f t="shared" si="0"/>
         <v>6117</v>
       </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I51">
+        <f t="shared" si="1"/>
+        <v>684</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" s="8">
         <v>9</v>
       </c>
@@ -7466,8 +8336,12 @@
         <f t="shared" si="0"/>
         <v>6830</v>
       </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I52">
+        <f t="shared" si="1"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" s="8">
         <v>10</v>
       </c>
@@ -7494,8 +8368,12 @@
         <f t="shared" si="0"/>
         <v>7543</v>
       </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I53">
+        <f t="shared" si="1"/>
+        <v>654</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" s="8">
         <v>11</v>
       </c>
@@ -7522,8 +8400,12 @@
         <f t="shared" si="0"/>
         <v>8256</v>
       </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I54">
+        <f t="shared" si="1"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" s="8">
         <v>12</v>
       </c>
@@ -7550,8 +8432,12 @@
         <f t="shared" si="0"/>
         <v>8969</v>
       </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I55">
+        <f t="shared" si="1"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" s="8">
         <v>13</v>
       </c>
@@ -7578,8 +8464,12 @@
         <f t="shared" si="0"/>
         <v>9683</v>
       </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I56">
+        <f t="shared" si="1"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" s="8">
         <v>14</v>
       </c>
@@ -7606,8 +8496,12 @@
         <f t="shared" si="0"/>
         <v>10642</v>
       </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I57">
+        <f t="shared" si="1"/>
+        <v>899</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" s="8">
         <v>1</v>
       </c>
@@ -7634,8 +8528,12 @@
         <f t="shared" si="0"/>
         <v>846</v>
       </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I58">
+        <f t="shared" si="1"/>
+        <v>660</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" s="8">
         <v>2</v>
       </c>
@@ -7662,8 +8560,12 @@
         <f t="shared" si="0"/>
         <v>1560</v>
       </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I59">
+        <f t="shared" si="1"/>
+        <v>654</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" s="8">
         <v>3</v>
       </c>
@@ -7690,8 +8592,12 @@
         <f t="shared" si="0"/>
         <v>2273</v>
       </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I60">
+        <f t="shared" si="1"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" s="8">
         <v>4</v>
       </c>
@@ -7718,8 +8624,12 @@
         <f t="shared" si="0"/>
         <v>2986</v>
       </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I61">
+        <f t="shared" si="1"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" s="8">
         <v>5</v>
       </c>
@@ -7746,8 +8656,12 @@
         <f t="shared" si="0"/>
         <v>3700</v>
       </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I62">
+        <f t="shared" si="1"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" s="8">
         <v>6</v>
       </c>
@@ -7774,8 +8688,12 @@
         <f t="shared" si="0"/>
         <v>4413</v>
       </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I63">
+        <f t="shared" si="1"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" s="8">
         <v>7</v>
       </c>
@@ -7802,8 +8720,12 @@
         <f t="shared" si="0"/>
         <v>5373</v>
       </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I64">
+        <f t="shared" si="1"/>
+        <v>900</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" s="8">
         <v>8</v>
       </c>
@@ -7830,8 +8752,12 @@
         <f t="shared" si="0"/>
         <v>6117</v>
       </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I65">
+        <f t="shared" si="1"/>
+        <v>684</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" s="8">
         <v>9</v>
       </c>
@@ -7858,8 +8784,12 @@
         <f t="shared" si="0"/>
         <v>6830</v>
       </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I66">
+        <f t="shared" si="1"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" s="8">
         <v>10</v>
       </c>
@@ -7879,15 +8809,19 @@
         <v>274</v>
       </c>
       <c r="G67" s="6">
-        <f t="shared" ref="G67:H113" si="1">LEFT(D67,2)*3600*30 + MID(D67,4,2)*60*30 + MID(D67,7,2)*30 + RIGHT(D67,2)</f>
+        <f t="shared" ref="G67:H113" si="2">LEFT(D67,2)*3600*30 + MID(D67,4,2)*60*30 + MID(D67,7,2)*30 + RIGHT(D67,2)</f>
         <v>6889</v>
       </c>
       <c r="H67" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7543</v>
       </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I67">
+        <f t="shared" ref="I67:I113" si="3">H67-G67</f>
+        <v>654</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" s="8">
         <v>11</v>
       </c>
@@ -7907,15 +8841,19 @@
         <v>275</v>
       </c>
       <c r="G68" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7603</v>
       </c>
       <c r="H68" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8256</v>
       </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I68">
+        <f t="shared" si="3"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" s="8">
         <v>12</v>
       </c>
@@ -7935,15 +8873,19 @@
         <v>274</v>
       </c>
       <c r="G69" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8316</v>
       </c>
       <c r="H69" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8969</v>
       </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I69">
+        <f t="shared" si="3"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" s="8">
         <v>13</v>
       </c>
@@ -7963,15 +8905,19 @@
         <v>275</v>
       </c>
       <c r="G70" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9030</v>
       </c>
       <c r="H70" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9683</v>
       </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I70">
+        <f t="shared" si="3"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" s="8">
         <v>14</v>
       </c>
@@ -7991,15 +8937,19 @@
         <v>283</v>
       </c>
       <c r="G71" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9743</v>
       </c>
       <c r="H71" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10642</v>
       </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I71">
+        <f t="shared" si="3"/>
+        <v>899</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" s="8">
         <v>1</v>
       </c>
@@ -8019,15 +8969,19 @@
         <v>274</v>
       </c>
       <c r="G72" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>186</v>
       </c>
       <c r="H72" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>846</v>
       </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I72">
+        <f t="shared" si="3"/>
+        <v>660</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" s="8">
         <v>2</v>
       </c>
@@ -8047,15 +9001,19 @@
         <v>275</v>
       </c>
       <c r="G73" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>906</v>
       </c>
       <c r="H73" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1560</v>
       </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I73">
+        <f t="shared" si="3"/>
+        <v>654</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" s="8">
         <v>3</v>
       </c>
@@ -8075,15 +9033,19 @@
         <v>274</v>
       </c>
       <c r="G74" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1620</v>
       </c>
       <c r="H74" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2273</v>
       </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I74">
+        <f t="shared" si="3"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" s="8">
         <v>4</v>
       </c>
@@ -8103,15 +9065,19 @@
         <v>275</v>
       </c>
       <c r="G75" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2333</v>
       </c>
       <c r="H75" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2986</v>
       </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I75">
+        <f t="shared" si="3"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" s="8">
         <v>5</v>
       </c>
@@ -8131,15 +9097,19 @@
         <v>274</v>
       </c>
       <c r="G76" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3047</v>
       </c>
       <c r="H76" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3700</v>
       </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I76">
+        <f t="shared" si="3"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" s="8">
         <v>6</v>
       </c>
@@ -8159,15 +9129,19 @@
         <v>275</v>
       </c>
       <c r="G77" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3760</v>
       </c>
       <c r="H77" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4413</v>
       </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I77">
+        <f t="shared" si="3"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" s="8">
         <v>7</v>
       </c>
@@ -8187,15 +9161,19 @@
         <v>284</v>
       </c>
       <c r="G78" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4473</v>
       </c>
       <c r="H78" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5373</v>
       </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I78">
+        <f t="shared" si="3"/>
+        <v>900</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" s="8">
         <v>8</v>
       </c>
@@ -8215,15 +9193,19 @@
         <v>274</v>
       </c>
       <c r="G79" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5433</v>
       </c>
       <c r="H79" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6117</v>
       </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I79">
+        <f t="shared" si="3"/>
+        <v>684</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" s="8">
         <v>9</v>
       </c>
@@ -8243,15 +9225,19 @@
         <v>275</v>
       </c>
       <c r="G80" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6177</v>
       </c>
       <c r="H80" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6830</v>
       </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I80">
+        <f t="shared" si="3"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" s="8">
         <v>10</v>
       </c>
@@ -8271,15 +9257,19 @@
         <v>274</v>
       </c>
       <c r="G81" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6889</v>
       </c>
       <c r="H81" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7543</v>
       </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I81">
+        <f t="shared" si="3"/>
+        <v>654</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82" s="8">
         <v>11</v>
       </c>
@@ -8299,15 +9289,19 @@
         <v>275</v>
       </c>
       <c r="G82" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7603</v>
       </c>
       <c r="H82" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8256</v>
       </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I82">
+        <f t="shared" si="3"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83" s="8">
         <v>12</v>
       </c>
@@ -8327,15 +9321,19 @@
         <v>274</v>
       </c>
       <c r="G83" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8316</v>
       </c>
       <c r="H83" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8969</v>
       </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I83">
+        <f t="shared" si="3"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84" s="8">
         <v>13</v>
       </c>
@@ -8355,15 +9353,19 @@
         <v>275</v>
       </c>
       <c r="G84" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9030</v>
       </c>
       <c r="H84" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9683</v>
       </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I84">
+        <f t="shared" si="3"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85" s="8">
         <v>14</v>
       </c>
@@ -8383,15 +9385,19 @@
         <v>280</v>
       </c>
       <c r="G85" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9743</v>
       </c>
       <c r="H85" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10642</v>
       </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I85">
+        <f t="shared" si="3"/>
+        <v>899</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A86" s="8">
         <v>1</v>
       </c>
@@ -8411,15 +9417,19 @@
         <v>275</v>
       </c>
       <c r="G86" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>186</v>
       </c>
       <c r="H86" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>846</v>
       </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I86">
+        <f t="shared" si="3"/>
+        <v>660</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A87" s="8">
         <v>2</v>
       </c>
@@ -8439,15 +9449,19 @@
         <v>274</v>
       </c>
       <c r="G87" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>906</v>
       </c>
       <c r="H87" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1560</v>
       </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I87">
+        <f t="shared" si="3"/>
+        <v>654</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A88" s="8">
         <v>3</v>
       </c>
@@ -8467,15 +9481,19 @@
         <v>275</v>
       </c>
       <c r="G88" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1620</v>
       </c>
       <c r="H88" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2273</v>
       </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I88">
+        <f t="shared" si="3"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A89" s="8">
         <v>4</v>
       </c>
@@ -8495,15 +9513,19 @@
         <v>274</v>
       </c>
       <c r="G89" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2333</v>
       </c>
       <c r="H89" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2986</v>
       </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I89">
+        <f t="shared" si="3"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A90" s="8">
         <v>5</v>
       </c>
@@ -8523,15 +9545,19 @@
         <v>275</v>
       </c>
       <c r="G90" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3047</v>
       </c>
       <c r="H90" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3700</v>
       </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I90">
+        <f t="shared" si="3"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A91" s="8">
         <v>6</v>
       </c>
@@ -8551,15 +9577,19 @@
         <v>274</v>
       </c>
       <c r="G91" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3760</v>
       </c>
       <c r="H91" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4413</v>
       </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I91">
+        <f t="shared" si="3"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A92" s="8">
         <v>7</v>
       </c>
@@ -8579,15 +9609,19 @@
         <v>285</v>
       </c>
       <c r="G92" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4473</v>
       </c>
       <c r="H92" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5373</v>
       </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I92">
+        <f t="shared" si="3"/>
+        <v>900</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93" s="8">
         <v>8</v>
       </c>
@@ -8607,15 +9641,19 @@
         <v>275</v>
       </c>
       <c r="G93" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5433</v>
       </c>
       <c r="H93" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6117</v>
       </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I93">
+        <f t="shared" si="3"/>
+        <v>684</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A94" s="8">
         <v>9</v>
       </c>
@@ -8635,15 +9673,19 @@
         <v>274</v>
       </c>
       <c r="G94" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6177</v>
       </c>
       <c r="H94" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6830</v>
       </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I94">
+        <f t="shared" si="3"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A95" s="8">
         <v>10</v>
       </c>
@@ -8663,15 +9705,19 @@
         <v>275</v>
       </c>
       <c r="G95" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6889</v>
       </c>
       <c r="H95" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7543</v>
       </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I95">
+        <f t="shared" si="3"/>
+        <v>654</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A96" s="8">
         <v>11</v>
       </c>
@@ -8691,15 +9737,19 @@
         <v>274</v>
       </c>
       <c r="G96" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7603</v>
       </c>
       <c r="H96" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8256</v>
       </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I96">
+        <f t="shared" si="3"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A97" s="8">
         <v>12</v>
       </c>
@@ -8719,15 +9769,19 @@
         <v>275</v>
       </c>
       <c r="G97" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8316</v>
       </c>
       <c r="H97" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8969</v>
       </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I97">
+        <f t="shared" si="3"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A98" s="8">
         <v>13</v>
       </c>
@@ -8747,15 +9801,19 @@
         <v>274</v>
       </c>
       <c r="G98" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9030</v>
       </c>
       <c r="H98" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9683</v>
       </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I98">
+        <f t="shared" si="3"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A99" s="8">
         <v>14</v>
       </c>
@@ -8775,15 +9833,19 @@
         <v>281</v>
       </c>
       <c r="G99" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9743</v>
       </c>
       <c r="H99" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10642</v>
       </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I99">
+        <f t="shared" si="3"/>
+        <v>899</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A100" s="8">
         <v>1</v>
       </c>
@@ -8803,15 +9865,19 @@
         <v>275</v>
       </c>
       <c r="G100" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>186</v>
       </c>
       <c r="H100" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>846</v>
       </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I100">
+        <f t="shared" si="3"/>
+        <v>660</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A101" s="8">
         <v>2</v>
       </c>
@@ -8831,15 +9897,19 @@
         <v>274</v>
       </c>
       <c r="G101" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>906</v>
       </c>
       <c r="H101" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1560</v>
       </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I101">
+        <f t="shared" si="3"/>
+        <v>654</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A102" s="8">
         <v>3</v>
       </c>
@@ -8859,15 +9929,19 @@
         <v>275</v>
       </c>
       <c r="G102" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1620</v>
       </c>
       <c r="H102" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2273</v>
       </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I102">
+        <f t="shared" si="3"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A103" s="8">
         <v>4</v>
       </c>
@@ -8887,15 +9961,19 @@
         <v>274</v>
       </c>
       <c r="G103" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2333</v>
       </c>
       <c r="H103" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2986</v>
       </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I103">
+        <f t="shared" si="3"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A104" s="8">
         <v>5</v>
       </c>
@@ -8915,15 +9993,19 @@
         <v>275</v>
       </c>
       <c r="G104" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3047</v>
       </c>
       <c r="H104" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3700</v>
       </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I104">
+        <f t="shared" si="3"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A105" s="8">
         <v>6</v>
       </c>
@@ -8943,15 +10025,19 @@
         <v>274</v>
       </c>
       <c r="G105" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3760</v>
       </c>
       <c r="H105" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4413</v>
       </c>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I105">
+        <f t="shared" si="3"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A106" s="8">
         <v>7</v>
       </c>
@@ -8971,15 +10057,19 @@
         <v>284</v>
       </c>
       <c r="G106" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4473</v>
       </c>
       <c r="H106" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5373</v>
       </c>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I106">
+        <f t="shared" si="3"/>
+        <v>900</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A107" s="8">
         <v>8</v>
       </c>
@@ -8999,15 +10089,19 @@
         <v>275</v>
       </c>
       <c r="G107" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5433</v>
       </c>
       <c r="H107" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6117</v>
       </c>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I107">
+        <f t="shared" si="3"/>
+        <v>684</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A108" s="8">
         <v>9</v>
       </c>
@@ -9027,15 +10121,19 @@
         <v>274</v>
       </c>
       <c r="G108" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6177</v>
       </c>
       <c r="H108" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6830</v>
       </c>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I108">
+        <f t="shared" si="3"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A109" s="8">
         <v>10</v>
       </c>
@@ -9055,15 +10153,19 @@
         <v>275</v>
       </c>
       <c r="G109" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6889</v>
       </c>
       <c r="H109" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7543</v>
       </c>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I109">
+        <f t="shared" si="3"/>
+        <v>654</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A110" s="8">
         <v>11</v>
       </c>
@@ -9083,15 +10185,19 @@
         <v>274</v>
       </c>
       <c r="G110" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7603</v>
       </c>
       <c r="H110" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8256</v>
       </c>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I110">
+        <f t="shared" si="3"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A111" s="8">
         <v>12</v>
       </c>
@@ -9111,15 +10217,19 @@
         <v>275</v>
       </c>
       <c r="G111" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8316</v>
       </c>
       <c r="H111" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8969</v>
       </c>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I111">
+        <f t="shared" si="3"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A112" s="8">
         <v>13</v>
       </c>
@@ -9139,15 +10249,19 @@
         <v>274</v>
       </c>
       <c r="G112" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9030</v>
       </c>
       <c r="H112" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9683</v>
       </c>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I112">
+        <f t="shared" si="3"/>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A113" s="8">
         <v>14</v>
       </c>
@@ -9167,15 +10281,19 @@
         <v>280</v>
       </c>
       <c r="G113" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9743</v>
       </c>
       <c r="H113" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10642</v>
       </c>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I113">
+        <f t="shared" si="3"/>
+        <v>899</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B114"/>
     </row>
   </sheetData>
@@ -9195,6 +10313,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001AAE30F29BC98549A6C45B45271C5A83" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="70fc1eee7aebc44ac40704a4c778e204">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6c0d6bb4-bf93-46e5-af3e-76fbe0d2898f" xmlns:ns3="cb5fc986-ca15-48a6-9872-3e00e06f3290" xmlns:ns4="897aa84e-6803-47c8-b68c-17d5fde4eba2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="84c483e3029d41a0188f1887cde70bc3" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="6c0d6bb4-bf93-46e5-af3e-76fbe0d2898f"/>
@@ -9460,15 +10587,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6730D68A-F459-44B9-B55A-08A4C6EDF8D4}">
   <ds:schemaRefs>
@@ -9488,6 +10606,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0CDED83-EA4E-4F36-A05F-0665C2CE98F5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D8C1EA4-A689-4448-B5CD-185A3AA72068}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9505,12 +10631,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0CDED83-EA4E-4F36-A05F-0665C2CE98F5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Aim2/Aim2_Data/aim2_timestamps_final.xlsx
+++ b/Aim2/Aim2_Data/aim2_timestamps_final.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eb255/Desktop/github/RISE/Aim2/Aim2_Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://chla.sharepoint.com/sites/BiostatsCore/Staff Files/My Vu/Elena Tenenbaum Aim 2/Updated_2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{863D1FB5-F92D-364A-BFA7-5CB1F6F7D9BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{69DE93BF-86AB-B240-AC14-9F3A5CEB7DB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01B90A16-03F0-2B4D-82E9-A7591FA9B944}"/>
   <bookViews>
-    <workbookView xWindow="440" yWindow="2000" windowWidth="28220" windowHeight="16180" activeTab="4" xr2:uid="{1905D5AD-B59A-4349-BC54-AD7B07C29ACC}"/>
+    <workbookView xWindow="440" yWindow="2000" windowWidth="28220" windowHeight="16180" activeTab="5" xr2:uid="{1905D5AD-B59A-4349-BC54-AD7B07C29ACC}"/>
   </bookViews>
   <sheets>
     <sheet name="GeoSocial" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1374" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1367" uniqueCount="286">
   <si>
     <t>Frame Start</t>
   </si>
@@ -900,9 +900,6 @@
   </si>
   <si>
     <t>blue left, yellow right</t>
-  </si>
-  <si>
-    <t>end_minus_start</t>
   </si>
 </sst>
 </file>
@@ -1328,7 +1325,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A723FD97-6B63-2843-8E5A-12061CB0C7C4}">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="19.5" customWidth="1"/>
@@ -1338,7 +1335,7 @@
     <col min="6" max="6" width="15.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1357,11 +1354,8 @@
       <c r="F1" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="4" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1382,12 +1376,8 @@
         <f>ROUND(D2*30,0)</f>
         <v>328</v>
       </c>
-      <c r="G2">
-        <f>F2-E2</f>
-        <v>147</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1408,12 +1398,8 @@
         <f t="shared" ref="F3:F11" si="1">ROUND(D3*30,0)</f>
         <v>480</v>
       </c>
-      <c r="G3">
-        <f>F3-E3</f>
-        <v>150</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1434,12 +1420,8 @@
         <f t="shared" si="1"/>
         <v>630</v>
       </c>
-      <c r="G4">
-        <f>F4-E4</f>
-        <v>149</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1460,12 +1442,8 @@
         <f t="shared" si="1"/>
         <v>780</v>
       </c>
-      <c r="G5">
-        <f>F5-E5</f>
-        <v>148</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1486,12 +1464,8 @@
         <f t="shared" si="1"/>
         <v>929</v>
       </c>
-      <c r="G6">
-        <f>F6-E6</f>
-        <v>148</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1512,12 +1486,8 @@
         <f t="shared" si="1"/>
         <v>1082</v>
       </c>
-      <c r="G7">
-        <f>F7-E7</f>
-        <v>152</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1538,12 +1508,8 @@
         <f t="shared" si="1"/>
         <v>1234</v>
       </c>
-      <c r="G8">
-        <f>F8-E8</f>
-        <v>151</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1564,12 +1530,8 @@
         <f t="shared" si="1"/>
         <v>1383</v>
       </c>
-      <c r="G9">
-        <f>F9-E9</f>
-        <v>148</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1590,12 +1552,8 @@
         <f t="shared" si="1"/>
         <v>1534</v>
       </c>
-      <c r="G10">
-        <f>F10-E10</f>
-        <v>150</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1615,10 +1573,6 @@
       <c r="F11">
         <f t="shared" si="1"/>
         <v>1720</v>
-      </c>
-      <c r="G11">
-        <f>F11-E11</f>
-        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -1628,14 +1582,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0569795-018A-454E-A86C-5367D9E0F514}">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.5" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="11.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1654,11 +1608,8 @@
       <c r="F1" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="4" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1679,12 +1630,8 @@
         <f>LEFT(D2,2)*3600*30 + MID(D2,4,2)*60*30 + MID(D2,7,2)*30 + RIGHT(D2,2)</f>
         <v>586</v>
       </c>
-      <c r="G2">
-        <f>F2-E2</f>
-        <v>399</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1705,12 +1652,8 @@
         <f t="shared" ref="F3:F7" si="1">LEFT(D3,2)*3600*30 + MID(D3,4,2)*60*30 + MID(D3,7,2)*30 + RIGHT(D3,2)</f>
         <v>1074</v>
       </c>
-      <c r="G3">
-        <f t="shared" ref="G3:G7" si="2">F3-E3</f>
-        <v>398</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1731,12 +1674,8 @@
         <f t="shared" si="1"/>
         <v>1564</v>
       </c>
-      <c r="G4">
-        <f t="shared" si="2"/>
-        <v>399</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1757,12 +1696,8 @@
         <f t="shared" si="1"/>
         <v>2055</v>
       </c>
-      <c r="G5">
-        <f t="shared" si="2"/>
-        <v>399</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1783,12 +1718,8 @@
         <f t="shared" si="1"/>
         <v>2546</v>
       </c>
-      <c r="G6">
-        <f t="shared" si="2"/>
-        <v>399</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1809,12 +1740,8 @@
         <f t="shared" si="1"/>
         <v>3038</v>
       </c>
-      <c r="G7">
-        <f t="shared" si="2"/>
-        <v>399</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
     </row>
@@ -1825,7 +1752,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF2C760A-3F0F-9B4C-B32C-F0DB99EEF92D}">
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.5" bestFit="1" customWidth="1"/>
@@ -1834,7 +1761,7 @@
     <col min="7" max="7" width="14.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1865,11 +1792,8 @@
       <c r="J1" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="4" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -1903,12 +1827,8 @@
         <f>H2+6</f>
         <v>75</v>
       </c>
-      <c r="K2">
-        <f>J2-I2</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -1942,12 +1862,8 @@
         <f t="shared" ref="J3:J17" si="2">H3+6</f>
         <v>195</v>
       </c>
-      <c r="K3">
-        <f t="shared" ref="K3:K17" si="3">J3-I3</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -1981,12 +1897,8 @@
         <f t="shared" si="2"/>
         <v>315</v>
       </c>
-      <c r="K4">
-        <f t="shared" si="3"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -2020,12 +1932,8 @@
         <f t="shared" si="2"/>
         <v>435</v>
       </c>
-      <c r="K5">
-        <f t="shared" si="3"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -2059,12 +1967,8 @@
         <f t="shared" si="2"/>
         <v>555</v>
       </c>
-      <c r="K6">
-        <f t="shared" si="3"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -2098,12 +2002,8 @@
         <f t="shared" si="2"/>
         <v>675</v>
       </c>
-      <c r="K7">
-        <f t="shared" si="3"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -2137,12 +2037,8 @@
         <f t="shared" si="2"/>
         <v>795</v>
       </c>
-      <c r="K8">
-        <f t="shared" si="3"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -2176,12 +2072,8 @@
         <f t="shared" si="2"/>
         <v>915</v>
       </c>
-      <c r="K9">
-        <f t="shared" si="3"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -2215,12 +2107,8 @@
         <f t="shared" si="2"/>
         <v>1035</v>
       </c>
-      <c r="K10">
-        <f t="shared" si="3"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -2254,12 +2142,8 @@
         <f t="shared" si="2"/>
         <v>1155</v>
       </c>
-      <c r="K11">
-        <f t="shared" si="3"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -2293,12 +2177,8 @@
         <f t="shared" si="2"/>
         <v>1275</v>
       </c>
-      <c r="K12">
-        <f t="shared" si="3"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -2332,12 +2212,8 @@
         <f t="shared" si="2"/>
         <v>1395</v>
       </c>
-      <c r="K13">
-        <f t="shared" si="3"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -2371,12 +2247,8 @@
         <f t="shared" si="2"/>
         <v>1515</v>
       </c>
-      <c r="K14">
-        <f t="shared" si="3"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -2410,12 +2282,8 @@
         <f t="shared" si="2"/>
         <v>1635</v>
       </c>
-      <c r="K15">
-        <f t="shared" si="3"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -2449,12 +2317,8 @@
         <f t="shared" si="2"/>
         <v>1755</v>
       </c>
-      <c r="K16">
-        <f t="shared" si="3"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -2487,10 +2351,6 @@
       <c r="J17">
         <f t="shared" si="2"/>
         <v>1875</v>
-      </c>
-      <c r="K17">
-        <f t="shared" si="3"/>
-        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -2500,7 +2360,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE25A399-0B6E-9F43-8135-606BE21B8DC7}">
-  <dimension ref="A1:M98"/>
+  <dimension ref="A1:M97"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.6640625" style="3" customWidth="1"/>
@@ -2543,9 +2403,7 @@
       <c r="H1" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="4" t="s">
-        <v>286</v>
-      </c>
+      <c r="I1"/>
       <c r="K1"/>
       <c r="M1"/>
     </row>
@@ -2576,10 +2434,7 @@
         <f>LEFT(F2,2)*3600*30 + MID(F2,4,2)*60*30 + MID(F2,7,2)*30 + RIGHT(F2,2)</f>
         <v>1397</v>
       </c>
-      <c r="I2">
-        <f>H2-G2</f>
-        <v>239</v>
-      </c>
+      <c r="I2" s="6"/>
       <c r="J2" s="4"/>
       <c r="K2" s="6"/>
       <c r="L2" s="4"/>
@@ -2612,10 +2467,7 @@
         <f t="shared" ref="H3:H32" si="1">LEFT(F3,2)*3600*30 + MID(F3,4,2)*60*30 + MID(F3,7,2)*30 + RIGHT(F3,2)</f>
         <v>1669</v>
       </c>
-      <c r="I3">
-        <f>H3-G3</f>
-        <v>239</v>
-      </c>
+      <c r="I3" s="6"/>
       <c r="J3" s="4"/>
       <c r="K3" s="6"/>
       <c r="L3" s="4"/>
@@ -2648,10 +2500,7 @@
         <f t="shared" si="1"/>
         <v>2843</v>
       </c>
-      <c r="I4">
-        <f>H4-G4</f>
-        <v>239</v>
-      </c>
+      <c r="I4" s="6"/>
       <c r="J4" s="4"/>
       <c r="K4" s="6"/>
       <c r="L4" s="4"/>
@@ -2684,10 +2533,7 @@
         <f t="shared" si="1"/>
         <v>3117</v>
       </c>
-      <c r="I5">
-        <f>H5-G5</f>
-        <v>239</v>
-      </c>
+      <c r="I5" s="6"/>
       <c r="J5" s="4"/>
       <c r="K5" s="6"/>
       <c r="L5" s="4"/>
@@ -2720,10 +2566,7 @@
         <f t="shared" si="1"/>
         <v>4285</v>
       </c>
-      <c r="I6">
-        <f>H6-G6</f>
-        <v>239</v>
-      </c>
+      <c r="I6" s="6"/>
       <c r="J6" s="4"/>
       <c r="K6" s="6"/>
       <c r="L6" s="4"/>
@@ -2756,10 +2599,7 @@
         <f t="shared" si="1"/>
         <v>4559</v>
       </c>
-      <c r="I7">
-        <f>H7-G7</f>
-        <v>239</v>
-      </c>
+      <c r="I7" s="6"/>
       <c r="J7" s="4"/>
       <c r="K7" s="6"/>
       <c r="L7" s="4"/>
@@ -2792,10 +2632,7 @@
         <f t="shared" si="1"/>
         <v>5703</v>
       </c>
-      <c r="I8">
-        <f>H8-G8</f>
-        <v>239</v>
-      </c>
+      <c r="I8" s="6"/>
       <c r="J8" s="4"/>
       <c r="K8" s="6"/>
       <c r="L8" s="4"/>
@@ -2828,10 +2665,7 @@
         <f t="shared" si="1"/>
         <v>6008</v>
       </c>
-      <c r="I9">
-        <f>H9-G9</f>
-        <v>240</v>
-      </c>
+      <c r="I9" s="6"/>
       <c r="J9" s="4"/>
       <c r="K9" s="6"/>
       <c r="L9" s="4"/>
@@ -2864,10 +2698,7 @@
         <f t="shared" si="1"/>
         <v>7145</v>
       </c>
-      <c r="I10">
-        <f>H10-G10</f>
-        <v>239</v>
-      </c>
+      <c r="I10" s="6"/>
       <c r="J10" s="4"/>
       <c r="K10" s="6"/>
       <c r="L10" s="4"/>
@@ -2900,10 +2731,7 @@
         <f t="shared" si="1"/>
         <v>7445</v>
       </c>
-      <c r="I11">
-        <f>H11-G11</f>
-        <v>239</v>
-      </c>
+      <c r="I11" s="6"/>
       <c r="J11" s="4"/>
       <c r="K11" s="6"/>
       <c r="L11" s="4"/>
@@ -2936,10 +2764,7 @@
         <f t="shared" si="1"/>
         <v>8585</v>
       </c>
-      <c r="I12">
-        <f>H12-G12</f>
-        <v>239</v>
-      </c>
+      <c r="I12" s="6"/>
       <c r="J12" s="4"/>
       <c r="K12" s="6"/>
       <c r="L12" s="4"/>
@@ -2972,10 +2797,7 @@
         <f t="shared" si="1"/>
         <v>8885</v>
       </c>
-      <c r="I13">
-        <f>H13-G13</f>
-        <v>239</v>
-      </c>
+      <c r="I13" s="7"/>
       <c r="K13" s="7"/>
       <c r="M13" s="7"/>
     </row>
@@ -3006,10 +2828,6 @@
         <f t="shared" si="1"/>
         <v>1397</v>
       </c>
-      <c r="I14">
-        <f>H14-G14</f>
-        <v>239</v>
-      </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
@@ -3038,10 +2856,6 @@
         <f t="shared" si="1"/>
         <v>1669</v>
       </c>
-      <c r="I15">
-        <f>H15-G15</f>
-        <v>239</v>
-      </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
@@ -3070,12 +2884,8 @@
         <f t="shared" si="1"/>
         <v>2845</v>
       </c>
-      <c r="I16">
-        <f>H16-G16</f>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>216</v>
       </c>
@@ -3102,12 +2912,8 @@
         <f t="shared" si="1"/>
         <v>3117</v>
       </c>
-      <c r="I17">
-        <f>H17-G17</f>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>217</v>
       </c>
@@ -3134,12 +2940,8 @@
         <f t="shared" si="1"/>
         <v>4263</v>
       </c>
-      <c r="I18">
-        <f>H18-G18</f>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>218</v>
       </c>
@@ -3166,12 +2968,8 @@
         <f t="shared" si="1"/>
         <v>4567</v>
       </c>
-      <c r="I19">
-        <f>H19-G19</f>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>219</v>
       </c>
@@ -3198,12 +2996,8 @@
         <f t="shared" si="1"/>
         <v>5715</v>
       </c>
-      <c r="I20">
-        <f>H20-G20</f>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>220</v>
       </c>
@@ -3230,12 +3024,8 @@
         <f t="shared" si="1"/>
         <v>6019</v>
       </c>
-      <c r="I21">
-        <f>H21-G21</f>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>221</v>
       </c>
@@ -3262,12 +3052,8 @@
         <f t="shared" si="1"/>
         <v>7165</v>
       </c>
-      <c r="I22">
-        <f>H22-G22</f>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>222</v>
       </c>
@@ -3294,12 +3080,8 @@
         <f t="shared" si="1"/>
         <v>7469</v>
       </c>
-      <c r="I23">
-        <f>H23-G23</f>
-        <v>269</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>223</v>
       </c>
@@ -3326,12 +3108,8 @@
         <f t="shared" si="1"/>
         <v>8613</v>
       </c>
-      <c r="I24">
-        <f>H24-G24</f>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>224</v>
       </c>
@@ -3358,12 +3136,8 @@
         <f t="shared" si="1"/>
         <v>8887</v>
       </c>
-      <c r="I25">
-        <f>H25-G25</f>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>213</v>
       </c>
@@ -3390,12 +3164,8 @@
         <f t="shared" si="1"/>
         <v>1391</v>
       </c>
-      <c r="I26">
-        <f>H26-G26</f>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>214</v>
       </c>
@@ -3422,12 +3192,8 @@
         <f t="shared" si="1"/>
         <v>1663</v>
       </c>
-      <c r="I27">
-        <f>H27-G27</f>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
         <v>215</v>
       </c>
@@ -3454,12 +3220,8 @@
         <f t="shared" si="1"/>
         <v>2837</v>
       </c>
-      <c r="I28">
-        <f>H28-G28</f>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
         <v>216</v>
       </c>
@@ -3486,12 +3248,8 @@
         <f t="shared" si="1"/>
         <v>3111</v>
       </c>
-      <c r="I29">
-        <f>H29-G29</f>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>217</v>
       </c>
@@ -3518,12 +3276,8 @@
         <f t="shared" si="1"/>
         <v>4283</v>
       </c>
-      <c r="I30">
-        <f>H30-G30</f>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
         <v>218</v>
       </c>
@@ -3550,12 +3304,8 @@
         <f t="shared" si="1"/>
         <v>4555</v>
       </c>
-      <c r="I31">
-        <f>H31-G31</f>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
         <v>219</v>
       </c>
@@ -3582,12 +3332,8 @@
         <f t="shared" si="1"/>
         <v>5727</v>
       </c>
-      <c r="I32">
-        <f>H32-G32</f>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
         <v>220</v>
       </c>
@@ -3614,12 +3360,8 @@
         <f>LEFT(F33,2)*3600*30 + MID(F33,4,2)*60*30 + MID(F33,7,2)*30 + RIGHT(F33,2)</f>
         <v>6001</v>
       </c>
-      <c r="I33">
-        <f t="shared" ref="I33:I96" si="2">H33-G33</f>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
         <v>221</v>
       </c>
@@ -3639,19 +3381,15 @@
         <v>115</v>
       </c>
       <c r="G34" s="6">
-        <f t="shared" ref="G34:G50" si="3">LEFT(E34,2)*3600*30 + MID(E34,4,2)*60*30 + MID(E34,7,2)*30 + RIGHT(E34,2)</f>
+        <f t="shared" ref="G34:G50" si="2">LEFT(E34,2)*3600*30 + MID(E34,4,2)*60*30 + MID(E34,7,2)*30 + RIGHT(E34,2)</f>
         <v>6904</v>
       </c>
       <c r="H34" s="6">
-        <f t="shared" ref="H34:H50" si="4">LEFT(F34,2)*3600*30 + MID(F34,4,2)*60*30 + MID(F34,7,2)*30 + RIGHT(F34,2)</f>
+        <f t="shared" ref="H34:H50" si="3">LEFT(F34,2)*3600*30 + MID(F34,4,2)*60*30 + MID(F34,7,2)*30 + RIGHT(F34,2)</f>
         <v>7143</v>
       </c>
-      <c r="I34">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
         <v>222</v>
       </c>
@@ -3671,19 +3409,15 @@
         <v>52</v>
       </c>
       <c r="G35" s="6">
+        <f t="shared" si="2"/>
+        <v>7206</v>
+      </c>
+      <c r="H35" s="6">
         <f t="shared" si="3"/>
-        <v>7206</v>
-      </c>
-      <c r="H35" s="6">
-        <f t="shared" si="4"/>
         <v>7445</v>
       </c>
-      <c r="I35">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
         <v>223</v>
       </c>
@@ -3703,19 +3437,15 @@
         <v>54</v>
       </c>
       <c r="G36" s="6">
+        <f t="shared" si="2"/>
+        <v>8346</v>
+      </c>
+      <c r="H36" s="6">
         <f t="shared" si="3"/>
-        <v>8346</v>
-      </c>
-      <c r="H36" s="6">
-        <f t="shared" si="4"/>
         <v>8585</v>
       </c>
-      <c r="I36">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
         <v>224</v>
       </c>
@@ -3735,19 +3465,15 @@
         <v>97</v>
       </c>
       <c r="G37" s="6">
+        <f t="shared" si="2"/>
+        <v>8648</v>
+      </c>
+      <c r="H37" s="6">
         <f t="shared" si="3"/>
-        <v>8648</v>
-      </c>
-      <c r="H37" s="6">
-        <f t="shared" si="4"/>
         <v>8887</v>
       </c>
-      <c r="I37">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
         <v>213</v>
       </c>
@@ -3767,19 +3493,15 @@
         <v>117</v>
       </c>
       <c r="G38" s="6">
+        <f t="shared" si="2"/>
+        <v>1162</v>
+      </c>
+      <c r="H38" s="6">
         <f t="shared" si="3"/>
-        <v>1162</v>
-      </c>
-      <c r="H38" s="6">
-        <f t="shared" si="4"/>
         <v>1401</v>
       </c>
-      <c r="I38">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
         <v>214</v>
       </c>
@@ -3799,19 +3521,15 @@
         <v>119</v>
       </c>
       <c r="G39" s="6">
+        <f t="shared" si="2"/>
+        <v>1434</v>
+      </c>
+      <c r="H39" s="6">
         <f t="shared" si="3"/>
-        <v>1434</v>
-      </c>
-      <c r="H39" s="6">
-        <f t="shared" si="4"/>
         <v>1673</v>
       </c>
-      <c r="I39">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
         <v>215</v>
       </c>
@@ -3831,19 +3549,15 @@
         <v>121</v>
       </c>
       <c r="G40" s="6">
+        <f t="shared" si="2"/>
+        <v>2608</v>
+      </c>
+      <c r="H40" s="6">
         <f t="shared" si="3"/>
-        <v>2608</v>
-      </c>
-      <c r="H40" s="6">
-        <f t="shared" si="4"/>
         <v>2847</v>
       </c>
-      <c r="I40">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
         <v>216</v>
       </c>
@@ -3863,19 +3577,15 @@
         <v>123</v>
       </c>
       <c r="G41" s="6">
+        <f t="shared" si="2"/>
+        <v>2880</v>
+      </c>
+      <c r="H41" s="6">
         <f t="shared" si="3"/>
-        <v>2880</v>
-      </c>
-      <c r="H41" s="6">
-        <f t="shared" si="4"/>
         <v>3119</v>
       </c>
-      <c r="I41">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
         <v>217</v>
       </c>
@@ -3895,19 +3605,15 @@
         <v>125</v>
       </c>
       <c r="G42" s="6">
+        <f t="shared" si="2"/>
+        <v>4022</v>
+      </c>
+      <c r="H42" s="6">
         <f t="shared" si="3"/>
-        <v>4022</v>
-      </c>
-      <c r="H42" s="6">
-        <f t="shared" si="4"/>
         <v>4261</v>
       </c>
-      <c r="I42">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
         <v>218</v>
       </c>
@@ -3927,19 +3633,15 @@
         <v>127</v>
       </c>
       <c r="G43" s="6">
+        <f t="shared" si="2"/>
+        <v>4326</v>
+      </c>
+      <c r="H43" s="6">
         <f t="shared" si="3"/>
-        <v>4326</v>
-      </c>
-      <c r="H43" s="6">
-        <f t="shared" si="4"/>
         <v>4565</v>
       </c>
-      <c r="I43">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
         <v>219</v>
       </c>
@@ -3959,19 +3661,15 @@
         <v>87</v>
       </c>
       <c r="G44" s="6">
+        <f t="shared" si="2"/>
+        <v>5476</v>
+      </c>
+      <c r="H44" s="6">
         <f t="shared" si="3"/>
-        <v>5476</v>
-      </c>
-      <c r="H44" s="6">
-        <f t="shared" si="4"/>
         <v>5715</v>
       </c>
-      <c r="I44">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
         <v>220</v>
       </c>
@@ -3991,19 +3689,15 @@
         <v>89</v>
       </c>
       <c r="G45" s="6">
+        <f t="shared" si="2"/>
+        <v>5780</v>
+      </c>
+      <c r="H45" s="6">
         <f t="shared" si="3"/>
-        <v>5780</v>
-      </c>
-      <c r="H45" s="6">
-        <f t="shared" si="4"/>
         <v>6019</v>
       </c>
-      <c r="I45">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
         <v>221</v>
       </c>
@@ -4023,19 +3717,15 @@
         <v>91</v>
       </c>
       <c r="G46" s="6">
+        <f t="shared" si="2"/>
+        <v>6926</v>
+      </c>
+      <c r="H46" s="6">
         <f t="shared" si="3"/>
-        <v>6926</v>
-      </c>
-      <c r="H46" s="6">
-        <f t="shared" si="4"/>
         <v>7165</v>
       </c>
-      <c r="I46">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
         <v>222</v>
       </c>
@@ -4055,19 +3745,15 @@
         <v>129</v>
       </c>
       <c r="G47" s="6">
+        <f t="shared" si="2"/>
+        <v>7228</v>
+      </c>
+      <c r="H47" s="6">
         <f t="shared" si="3"/>
-        <v>7228</v>
-      </c>
-      <c r="H47" s="6">
-        <f t="shared" si="4"/>
         <v>7467</v>
       </c>
-      <c r="I47">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
         <v>223</v>
       </c>
@@ -4087,19 +3773,15 @@
         <v>95</v>
       </c>
       <c r="G48" s="6">
+        <f t="shared" si="2"/>
+        <v>8374</v>
+      </c>
+      <c r="H48" s="6">
         <f t="shared" si="3"/>
-        <v>8374</v>
-      </c>
-      <c r="H48" s="6">
-        <f t="shared" si="4"/>
         <v>8613</v>
       </c>
-      <c r="I48">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
         <v>224</v>
       </c>
@@ -4119,19 +3801,15 @@
         <v>97</v>
       </c>
       <c r="G49" s="6">
+        <f t="shared" si="2"/>
+        <v>8648</v>
+      </c>
+      <c r="H49" s="6">
         <f t="shared" si="3"/>
-        <v>8648</v>
-      </c>
-      <c r="H49" s="6">
-        <f t="shared" si="4"/>
         <v>8887</v>
       </c>
-      <c r="I49">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
         <v>213</v>
       </c>
@@ -4151,19 +3829,15 @@
         <v>131</v>
       </c>
       <c r="G50" s="6">
+        <f t="shared" si="2"/>
+        <v>1156</v>
+      </c>
+      <c r="H50" s="6">
         <f t="shared" si="3"/>
-        <v>1156</v>
-      </c>
-      <c r="H50" s="6">
-        <f t="shared" si="4"/>
         <v>1395</v>
       </c>
-      <c r="I50">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
         <v>214</v>
       </c>
@@ -4190,12 +3864,8 @@
         <f>LEFT(F51,2)*3600*30 + MID(F51,4,2)*60*30 + MID(F51,7,2)*30 + RIGHT(F51,2)</f>
         <v>1667</v>
       </c>
-      <c r="I51">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
         <v>215</v>
       </c>
@@ -4215,19 +3885,15 @@
         <v>135</v>
       </c>
       <c r="G52" s="6">
-        <f t="shared" ref="G52:G71" si="5">LEFT(E52,2)*3600*30 + MID(E52,4,2)*60*30 + MID(E52,7,2)*30 + RIGHT(E52,2)</f>
+        <f t="shared" ref="G52:G71" si="4">LEFT(E52,2)*3600*30 + MID(E52,4,2)*60*30 + MID(E52,7,2)*30 + RIGHT(E52,2)</f>
         <v>2600</v>
       </c>
       <c r="H52" s="6">
-        <f t="shared" ref="H52:H71" si="6">LEFT(F52,2)*3600*30 + MID(F52,4,2)*60*30 + MID(F52,7,2)*30 + RIGHT(F52,2)</f>
+        <f t="shared" ref="H52:H71" si="5">LEFT(F52,2)*3600*30 + MID(F52,4,2)*60*30 + MID(F52,7,2)*30 + RIGHT(F52,2)</f>
         <v>2839</v>
       </c>
-      <c r="I52">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
         <v>216</v>
       </c>
@@ -4247,19 +3913,15 @@
         <v>105</v>
       </c>
       <c r="G53" s="6">
+        <f t="shared" si="4"/>
+        <v>2872</v>
+      </c>
+      <c r="H53" s="6">
         <f t="shared" si="5"/>
-        <v>2872</v>
-      </c>
-      <c r="H53" s="6">
-        <f t="shared" si="6"/>
         <v>3111</v>
       </c>
-      <c r="I53">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
         <v>217</v>
       </c>
@@ -4279,19 +3941,15 @@
         <v>137</v>
       </c>
       <c r="G54" s="6">
+        <f t="shared" si="4"/>
+        <v>4042</v>
+      </c>
+      <c r="H54" s="6">
         <f t="shared" si="5"/>
-        <v>4042</v>
-      </c>
-      <c r="H54" s="6">
-        <f t="shared" si="6"/>
         <v>4281</v>
       </c>
-      <c r="I54">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
         <v>218</v>
       </c>
@@ -4311,19 +3969,15 @@
         <v>139</v>
       </c>
       <c r="G55" s="6">
+        <f t="shared" si="4"/>
+        <v>4314</v>
+      </c>
+      <c r="H55" s="6">
         <f t="shared" si="5"/>
-        <v>4314</v>
-      </c>
-      <c r="H55" s="6">
-        <f t="shared" si="6"/>
         <v>4553</v>
       </c>
-      <c r="I55">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
         <v>219</v>
       </c>
@@ -4343,19 +3997,15 @@
         <v>141</v>
       </c>
       <c r="G56" s="6">
+        <f t="shared" si="4"/>
+        <v>5484</v>
+      </c>
+      <c r="H56" s="6">
         <f t="shared" si="5"/>
-        <v>5484</v>
-      </c>
-      <c r="H56" s="6">
-        <f t="shared" si="6"/>
         <v>5723</v>
       </c>
-      <c r="I56">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="4" t="s">
         <v>220</v>
       </c>
@@ -4375,19 +4025,15 @@
         <v>143</v>
       </c>
       <c r="G57" s="6">
+        <f t="shared" si="4"/>
+        <v>5754</v>
+      </c>
+      <c r="H57" s="6">
         <f t="shared" si="5"/>
-        <v>5754</v>
-      </c>
-      <c r="H57" s="6">
-        <f t="shared" si="6"/>
         <v>5993</v>
       </c>
-      <c r="I57">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
         <v>221</v>
       </c>
@@ -4407,19 +4053,15 @@
         <v>145</v>
       </c>
       <c r="G58" s="6">
+        <f t="shared" si="4"/>
+        <v>6926</v>
+      </c>
+      <c r="H58" s="6">
         <f t="shared" si="5"/>
-        <v>6926</v>
-      </c>
-      <c r="H58" s="6">
-        <f t="shared" si="6"/>
         <v>7165</v>
       </c>
-      <c r="I58">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="4" t="s">
         <v>222</v>
       </c>
@@ -4439,19 +4081,15 @@
         <v>147</v>
       </c>
       <c r="G59" s="6">
+        <f t="shared" si="4"/>
+        <v>7198</v>
+      </c>
+      <c r="H59" s="6">
         <f t="shared" si="5"/>
-        <v>7198</v>
-      </c>
-      <c r="H59" s="6">
-        <f t="shared" si="6"/>
         <v>7437</v>
       </c>
-      <c r="I59">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
         <v>223</v>
       </c>
@@ -4471,19 +4109,15 @@
         <v>149</v>
       </c>
       <c r="G60" s="6">
+        <f t="shared" si="4"/>
+        <v>8368</v>
+      </c>
+      <c r="H60" s="6">
         <f t="shared" si="5"/>
-        <v>8368</v>
-      </c>
-      <c r="H60" s="6">
-        <f t="shared" si="6"/>
         <v>8608</v>
       </c>
-      <c r="I60">
-        <f t="shared" si="2"/>
-        <v>240</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
         <v>224</v>
       </c>
@@ -4503,19 +4137,15 @@
         <v>151</v>
       </c>
       <c r="G61" s="6">
+        <f t="shared" si="4"/>
+        <v>8638</v>
+      </c>
+      <c r="H61" s="6">
         <f t="shared" si="5"/>
-        <v>8638</v>
-      </c>
-      <c r="H61" s="6">
-        <f t="shared" si="6"/>
         <v>8877</v>
       </c>
-      <c r="I61">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
         <v>213</v>
       </c>
@@ -4535,19 +4165,15 @@
         <v>99</v>
       </c>
       <c r="G62" s="6">
+        <f t="shared" si="4"/>
+        <v>1152</v>
+      </c>
+      <c r="H62" s="6">
         <f t="shared" si="5"/>
-        <v>1152</v>
-      </c>
-      <c r="H62" s="6">
-        <f t="shared" si="6"/>
         <v>1391</v>
       </c>
-      <c r="I62">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
         <v>214</v>
       </c>
@@ -4567,19 +4193,15 @@
         <v>101</v>
       </c>
       <c r="G63" s="6">
+        <f t="shared" si="4"/>
+        <v>1424</v>
+      </c>
+      <c r="H63" s="6">
         <f t="shared" si="5"/>
-        <v>1424</v>
-      </c>
-      <c r="H63" s="6">
-        <f t="shared" si="6"/>
         <v>1663</v>
       </c>
-      <c r="I63">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
         <v>215</v>
       </c>
@@ -4599,19 +4221,15 @@
         <v>103</v>
       </c>
       <c r="G64" s="6">
+        <f t="shared" si="4"/>
+        <v>2598</v>
+      </c>
+      <c r="H64" s="6">
         <f t="shared" si="5"/>
-        <v>2598</v>
-      </c>
-      <c r="H64" s="6">
-        <f t="shared" si="6"/>
         <v>2837</v>
       </c>
-      <c r="I64">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="4" t="s">
         <v>216</v>
       </c>
@@ -4631,19 +4249,15 @@
         <v>105</v>
       </c>
       <c r="G65" s="6">
+        <f t="shared" si="4"/>
+        <v>2872</v>
+      </c>
+      <c r="H65" s="6">
         <f t="shared" si="5"/>
-        <v>2872</v>
-      </c>
-      <c r="H65" s="6">
-        <f t="shared" si="6"/>
         <v>3111</v>
       </c>
-      <c r="I65">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
         <v>217</v>
       </c>
@@ -4663,19 +4277,15 @@
         <v>107</v>
       </c>
       <c r="G66" s="6">
+        <f t="shared" si="4"/>
+        <v>4044</v>
+      </c>
+      <c r="H66" s="6">
         <f t="shared" si="5"/>
-        <v>4044</v>
-      </c>
-      <c r="H66" s="6">
-        <f t="shared" si="6"/>
         <v>4283</v>
       </c>
-      <c r="I66">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="4" t="s">
         <v>218</v>
       </c>
@@ -4695,19 +4305,15 @@
         <v>109</v>
       </c>
       <c r="G67" s="6">
+        <f t="shared" si="4"/>
+        <v>4316</v>
+      </c>
+      <c r="H67" s="6">
         <f t="shared" si="5"/>
-        <v>4316</v>
-      </c>
-      <c r="H67" s="6">
-        <f t="shared" si="6"/>
         <v>4555</v>
       </c>
-      <c r="I67">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="4" t="s">
         <v>219</v>
       </c>
@@ -4727,19 +4333,15 @@
         <v>153</v>
       </c>
       <c r="G68" s="6">
+        <f t="shared" si="4"/>
+        <v>5460</v>
+      </c>
+      <c r="H68" s="6">
         <f t="shared" si="5"/>
-        <v>5460</v>
-      </c>
-      <c r="H68" s="6">
-        <f t="shared" si="6"/>
         <v>5699</v>
       </c>
-      <c r="I68">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="4" t="s">
         <v>220</v>
       </c>
@@ -4759,19 +4361,15 @@
         <v>155</v>
       </c>
       <c r="G69" s="6">
+        <f t="shared" si="4"/>
+        <v>5734</v>
+      </c>
+      <c r="H69" s="6">
         <f t="shared" si="5"/>
-        <v>5734</v>
-      </c>
-      <c r="H69" s="6">
-        <f t="shared" si="6"/>
         <v>5973</v>
       </c>
-      <c r="I69">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="4" t="s">
         <v>221</v>
       </c>
@@ -4791,19 +4389,15 @@
         <v>157</v>
       </c>
       <c r="G70" s="6">
+        <f t="shared" si="4"/>
+        <v>6904</v>
+      </c>
+      <c r="H70" s="6">
         <f t="shared" si="5"/>
-        <v>6904</v>
-      </c>
-      <c r="H70" s="6">
-        <f t="shared" si="6"/>
         <v>7143</v>
       </c>
-      <c r="I70">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="4" t="s">
         <v>222</v>
       </c>
@@ -4823,19 +4417,15 @@
         <v>159</v>
       </c>
       <c r="G71" s="6">
+        <f t="shared" si="4"/>
+        <v>7176</v>
+      </c>
+      <c r="H71" s="6">
         <f t="shared" si="5"/>
-        <v>7176</v>
-      </c>
-      <c r="H71" s="6">
-        <f t="shared" si="6"/>
         <v>7415</v>
       </c>
-      <c r="I71">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="4" t="s">
         <v>223</v>
       </c>
@@ -4862,12 +4452,8 @@
         <f>LEFT(F72,2)*3600*30 + MID(F72,4,2)*60*30 + MID(F72,7,2)*30 + RIGHT(F72,2)</f>
         <v>8587</v>
       </c>
-      <c r="I72">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" s="4" t="s">
         <v>224</v>
       </c>
@@ -4887,19 +4473,15 @@
         <v>163</v>
       </c>
       <c r="G73" s="6">
-        <f t="shared" ref="G73:G84" si="7">LEFT(E73,2)*3600*30 + MID(E73,4,2)*60*30 + MID(E73,7,2)*30 + RIGHT(E73,2)</f>
+        <f t="shared" ref="G73:G84" si="6">LEFT(E73,2)*3600*30 + MID(E73,4,2)*60*30 + MID(E73,7,2)*30 + RIGHT(E73,2)</f>
         <v>8620</v>
       </c>
       <c r="H73" s="6">
-        <f t="shared" ref="H73:H84" si="8">LEFT(F73,2)*3600*30 + MID(F73,4,2)*60*30 + MID(F73,7,2)*30 + RIGHT(F73,2)</f>
+        <f t="shared" ref="H73:H84" si="7">LEFT(F73,2)*3600*30 + MID(F73,4,2)*60*30 + MID(F73,7,2)*30 + RIGHT(F73,2)</f>
         <v>8859</v>
       </c>
-      <c r="I73">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" s="4" t="s">
         <v>213</v>
       </c>
@@ -4919,19 +4501,15 @@
         <v>165</v>
       </c>
       <c r="G74" s="6">
+        <f t="shared" si="6"/>
+        <v>1160</v>
+      </c>
+      <c r="H74" s="6">
         <f t="shared" si="7"/>
-        <v>1160</v>
-      </c>
-      <c r="H74" s="6">
-        <f t="shared" si="8"/>
         <v>1399</v>
       </c>
-      <c r="I74">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" s="4" t="s">
         <v>214</v>
       </c>
@@ -4951,19 +4529,15 @@
         <v>167</v>
       </c>
       <c r="G75" s="6">
+        <f t="shared" si="6"/>
+        <v>1432</v>
+      </c>
+      <c r="H75" s="6">
         <f t="shared" si="7"/>
-        <v>1432</v>
-      </c>
-      <c r="H75" s="6">
-        <f t="shared" si="8"/>
         <v>1671</v>
       </c>
-      <c r="I75">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" s="4" t="s">
         <v>215</v>
       </c>
@@ -4983,19 +4557,15 @@
         <v>38</v>
       </c>
       <c r="G76" s="6">
+        <f t="shared" si="6"/>
+        <v>2604</v>
+      </c>
+      <c r="H76" s="6">
         <f t="shared" si="7"/>
-        <v>2604</v>
-      </c>
-      <c r="H76" s="6">
-        <f t="shared" si="8"/>
         <v>2843</v>
       </c>
-      <c r="I76">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" s="4" t="s">
         <v>216</v>
       </c>
@@ -5015,19 +4585,15 @@
         <v>169</v>
       </c>
       <c r="G77" s="6">
+        <f t="shared" si="6"/>
+        <v>2876</v>
+      </c>
+      <c r="H77" s="6">
         <f t="shared" si="7"/>
-        <v>2876</v>
-      </c>
-      <c r="H77" s="6">
-        <f t="shared" si="8"/>
         <v>3115</v>
       </c>
-      <c r="I77">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" s="4" t="s">
         <v>217</v>
       </c>
@@ -5047,19 +4613,15 @@
         <v>83</v>
       </c>
       <c r="G78" s="6">
+        <f t="shared" si="6"/>
+        <v>4024</v>
+      </c>
+      <c r="H78" s="6">
         <f t="shared" si="7"/>
-        <v>4024</v>
-      </c>
-      <c r="H78" s="6">
-        <f t="shared" si="8"/>
         <v>4263</v>
       </c>
-      <c r="I78">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" s="4" t="s">
         <v>218</v>
       </c>
@@ -5079,19 +4641,15 @@
         <v>127</v>
       </c>
       <c r="G79" s="6">
+        <f t="shared" si="6"/>
+        <v>4326</v>
+      </c>
+      <c r="H79" s="6">
         <f t="shared" si="7"/>
-        <v>4326</v>
-      </c>
-      <c r="H79" s="6">
-        <f t="shared" si="8"/>
         <v>4565</v>
       </c>
-      <c r="I79">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" s="4" t="s">
         <v>219</v>
       </c>
@@ -5111,19 +4669,15 @@
         <v>171</v>
       </c>
       <c r="G80" s="6">
+        <f t="shared" si="6"/>
+        <v>5468</v>
+      </c>
+      <c r="H80" s="6">
         <f t="shared" si="7"/>
-        <v>5468</v>
-      </c>
-      <c r="H80" s="6">
-        <f t="shared" si="8"/>
         <v>5707</v>
       </c>
-      <c r="I80">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" s="4" t="s">
         <v>220</v>
       </c>
@@ -5143,19 +4697,15 @@
         <v>173</v>
       </c>
       <c r="G81" s="6">
+        <f t="shared" si="6"/>
+        <v>5770</v>
+      </c>
+      <c r="H81" s="6">
         <f t="shared" si="7"/>
-        <v>5770</v>
-      </c>
-      <c r="H81" s="6">
-        <f t="shared" si="8"/>
         <v>6009</v>
       </c>
-      <c r="I81">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" s="4" t="s">
         <v>221</v>
       </c>
@@ -5175,19 +4725,15 @@
         <v>175</v>
       </c>
       <c r="G82" s="6">
+        <f t="shared" si="6"/>
+        <v>6914</v>
+      </c>
+      <c r="H82" s="6">
         <f t="shared" si="7"/>
-        <v>6914</v>
-      </c>
-      <c r="H82" s="6">
-        <f t="shared" si="8"/>
         <v>7153</v>
       </c>
-      <c r="I82">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" s="4" t="s">
         <v>222</v>
       </c>
@@ -5207,19 +4753,15 @@
         <v>177</v>
       </c>
       <c r="G83" s="6">
+        <f t="shared" si="6"/>
+        <v>7216</v>
+      </c>
+      <c r="H83" s="6">
         <f t="shared" si="7"/>
-        <v>7216</v>
-      </c>
-      <c r="H83" s="6">
-        <f t="shared" si="8"/>
         <v>7455</v>
       </c>
-      <c r="I83">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" s="4" t="s">
         <v>223</v>
       </c>
@@ -5239,19 +4781,15 @@
         <v>179</v>
       </c>
       <c r="G84" s="6">
+        <f t="shared" si="6"/>
+        <v>8356</v>
+      </c>
+      <c r="H84" s="6">
         <f t="shared" si="7"/>
-        <v>8356</v>
-      </c>
-      <c r="H84" s="6">
-        <f t="shared" si="8"/>
         <v>8595</v>
       </c>
-      <c r="I84">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" s="4" t="s">
         <v>224</v>
       </c>
@@ -5278,12 +4816,8 @@
         <f>LEFT(F85,2)*3600*30 + MID(F85,4,2)*60*30 + MID(F85,7,2)*30 + RIGHT(F85,2)</f>
         <v>8897</v>
       </c>
-      <c r="I85">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" s="4" t="s">
         <v>213</v>
       </c>
@@ -5303,19 +4837,15 @@
         <v>34</v>
       </c>
       <c r="G86" s="6">
-        <f t="shared" ref="G86:G97" si="9">LEFT(E86,2)*3600*30 + MID(E86,4,2)*60*30 + MID(E86,7,2)*30 + RIGHT(E86,2)</f>
+        <f t="shared" ref="G86:G97" si="8">LEFT(E86,2)*3600*30 + MID(E86,4,2)*60*30 + MID(E86,7,2)*30 + RIGHT(E86,2)</f>
         <v>1158</v>
       </c>
       <c r="H86" s="6">
-        <f t="shared" ref="H86:H97" si="10">LEFT(F86,2)*3600*30 + MID(F86,4,2)*60*30 + MID(F86,7,2)*30 + RIGHT(F86,2)</f>
+        <f t="shared" ref="H86:H97" si="9">LEFT(F86,2)*3600*30 + MID(F86,4,2)*60*30 + MID(F86,7,2)*30 + RIGHT(F86,2)</f>
         <v>1397</v>
       </c>
-      <c r="I86">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" s="4" t="s">
         <v>214</v>
       </c>
@@ -5335,19 +4865,15 @@
         <v>36</v>
       </c>
       <c r="G87" s="6">
+        <f t="shared" si="8"/>
+        <v>1430</v>
+      </c>
+      <c r="H87" s="6">
         <f t="shared" si="9"/>
-        <v>1430</v>
-      </c>
-      <c r="H87" s="6">
-        <f t="shared" si="10"/>
         <v>1669</v>
       </c>
-      <c r="I87">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" s="4" t="s">
         <v>215</v>
       </c>
@@ -5367,19 +4893,15 @@
         <v>183</v>
       </c>
       <c r="G88" s="6">
+        <f t="shared" si="8"/>
+        <v>2580</v>
+      </c>
+      <c r="H88" s="6">
         <f t="shared" si="9"/>
-        <v>2580</v>
-      </c>
-      <c r="H88" s="6">
-        <f t="shared" si="10"/>
         <v>2849</v>
       </c>
-      <c r="I88">
-        <f t="shared" si="2"/>
-        <v>269</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" s="4" t="s">
         <v>216</v>
       </c>
@@ -5399,19 +4921,15 @@
         <v>185</v>
       </c>
       <c r="G89" s="6">
+        <f t="shared" si="8"/>
+        <v>2882</v>
+      </c>
+      <c r="H89" s="6">
         <f t="shared" si="9"/>
-        <v>2882</v>
-      </c>
-      <c r="H89" s="6">
-        <f t="shared" si="10"/>
         <v>3121</v>
       </c>
-      <c r="I89">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" s="4" t="s">
         <v>217</v>
       </c>
@@ -5431,19 +4949,15 @@
         <v>187</v>
       </c>
       <c r="G90" s="6">
+        <f t="shared" si="8"/>
+        <v>4030</v>
+      </c>
+      <c r="H90" s="6">
         <f t="shared" si="9"/>
-        <v>4030</v>
-      </c>
-      <c r="H90" s="6">
-        <f t="shared" si="10"/>
         <v>4269</v>
       </c>
-      <c r="I90">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" s="4" t="s">
         <v>218</v>
       </c>
@@ -5463,19 +4977,15 @@
         <v>189</v>
       </c>
       <c r="G91" s="6">
+        <f t="shared" si="8"/>
+        <v>4332</v>
+      </c>
+      <c r="H91" s="6">
         <f t="shared" si="9"/>
-        <v>4332</v>
-      </c>
-      <c r="H91" s="6">
-        <f t="shared" si="10"/>
         <v>4571</v>
       </c>
-      <c r="I91">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" s="4" t="s">
         <v>219</v>
       </c>
@@ -5495,19 +5005,15 @@
         <v>191</v>
       </c>
       <c r="G92" s="6">
+        <f t="shared" si="8"/>
+        <v>5480</v>
+      </c>
+      <c r="H92" s="6">
         <f t="shared" si="9"/>
-        <v>5480</v>
-      </c>
-      <c r="H92" s="6">
-        <f t="shared" si="10"/>
         <v>5719</v>
       </c>
-      <c r="I92">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" s="4" t="s">
         <v>220</v>
       </c>
@@ -5527,19 +5033,15 @@
         <v>193</v>
       </c>
       <c r="G93" s="6">
+        <f t="shared" si="8"/>
+        <v>5782</v>
+      </c>
+      <c r="H93" s="6">
         <f t="shared" si="9"/>
-        <v>5782</v>
-      </c>
-      <c r="H93" s="6">
-        <f t="shared" si="10"/>
         <v>6021</v>
       </c>
-      <c r="I93">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" s="4" t="s">
         <v>221</v>
       </c>
@@ -5559,19 +5061,15 @@
         <v>195</v>
       </c>
       <c r="G94" s="6">
+        <f t="shared" si="8"/>
+        <v>6924</v>
+      </c>
+      <c r="H94" s="6">
         <f t="shared" si="9"/>
-        <v>6924</v>
-      </c>
-      <c r="H94" s="6">
-        <f t="shared" si="10"/>
         <v>7163</v>
       </c>
-      <c r="I94">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" s="4" t="s">
         <v>222</v>
       </c>
@@ -5591,19 +5089,15 @@
         <v>197</v>
       </c>
       <c r="G95" s="6">
+        <f t="shared" si="8"/>
+        <v>7226</v>
+      </c>
+      <c r="H95" s="6">
         <f t="shared" si="9"/>
-        <v>7226</v>
-      </c>
-      <c r="H95" s="6">
-        <f t="shared" si="10"/>
         <v>7465</v>
       </c>
-      <c r="I95">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" s="4" t="s">
         <v>223</v>
       </c>
@@ -5623,19 +5117,15 @@
         <v>199</v>
       </c>
       <c r="G96" s="6">
+        <f t="shared" si="8"/>
+        <v>8366</v>
+      </c>
+      <c r="H96" s="6">
         <f t="shared" si="9"/>
-        <v>8366</v>
-      </c>
-      <c r="H96" s="6">
-        <f t="shared" si="10"/>
         <v>8605</v>
       </c>
-      <c r="I96">
-        <f t="shared" si="2"/>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" s="4" t="s">
         <v>224</v>
       </c>
@@ -5655,20 +5145,13 @@
         <v>201</v>
       </c>
       <c r="G97" s="6">
+        <f t="shared" si="8"/>
+        <v>8668</v>
+      </c>
+      <c r="H97" s="6">
         <f t="shared" si="9"/>
-        <v>8668</v>
-      </c>
-      <c r="H97" s="6">
-        <f t="shared" si="10"/>
         <v>8907</v>
       </c>
-      <c r="I97">
-        <f t="shared" ref="I97" si="11">H97-G97</f>
-        <v>239</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="I98"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5677,14 +5160,14 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{406840D2-2351-0442-B27E-76241ED21B09}">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="18.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -5700,11 +5183,8 @@
       <c r="E1" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5720,12 +5200,8 @@
       <c r="E2" s="1">
         <v>310</v>
       </c>
-      <c r="F2">
-        <f>E2-D2</f>
-        <v>79</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -5741,12 +5217,8 @@
       <c r="E3" s="1">
         <v>520</v>
       </c>
-      <c r="F3">
-        <f t="shared" ref="F3:F21" si="0">E3-D3</f>
-        <v>89</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -5762,12 +5234,8 @@
       <c r="E4" s="1">
         <v>730</v>
       </c>
-      <c r="F4">
-        <f t="shared" si="0"/>
-        <v>68</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -5783,12 +5251,8 @@
       <c r="E5" s="1">
         <v>940</v>
       </c>
-      <c r="F5">
-        <f t="shared" si="0"/>
-        <v>90</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -5804,12 +5268,8 @@
       <c r="E6" s="1">
         <v>1150</v>
       </c>
-      <c r="F6">
-        <f t="shared" si="0"/>
-        <v>85</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -5825,12 +5285,8 @@
       <c r="E7" s="1">
         <v>1360</v>
       </c>
-      <c r="F7">
-        <f t="shared" si="0"/>
-        <v>87</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -5846,12 +5302,8 @@
       <c r="E8" s="1">
         <v>1570</v>
       </c>
-      <c r="F8">
-        <f t="shared" si="0"/>
-        <v>77</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -5867,12 +5319,8 @@
       <c r="E9" s="1">
         <v>1780</v>
       </c>
-      <c r="F9">
-        <f t="shared" si="0"/>
-        <v>78</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -5888,12 +5336,8 @@
       <c r="E10" s="1">
         <v>1990</v>
       </c>
-      <c r="F10">
-        <f t="shared" si="0"/>
-        <v>88</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -5909,12 +5353,8 @@
       <c r="E11" s="1">
         <v>2201</v>
       </c>
-      <c r="F11">
-        <f t="shared" si="0"/>
-        <v>84</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12">
         <f>A11+1</f>
         <v>11</v>
@@ -5931,14 +5371,10 @@
       <c r="E12" s="1">
         <v>2412</v>
       </c>
-      <c r="F12">
-        <f t="shared" si="0"/>
-        <v>87</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13">
-        <f t="shared" ref="A13:A21" si="1">A12+1</f>
+        <f t="shared" ref="A13:A21" si="0">A12+1</f>
         <v>12</v>
       </c>
       <c r="B13" t="s">
@@ -5953,14 +5389,10 @@
       <c r="E13" s="1">
         <v>2622</v>
       </c>
-      <c r="F13">
-        <f t="shared" si="0"/>
-        <v>86</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B14" t="s">
@@ -5975,14 +5407,10 @@
       <c r="E14" s="1">
         <v>2832</v>
       </c>
-      <c r="F14">
-        <f t="shared" si="0"/>
-        <v>84</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B15" t="s">
@@ -5997,14 +5425,10 @@
       <c r="E15" s="1">
         <v>3042</v>
       </c>
-      <c r="F15">
-        <f t="shared" si="0"/>
-        <v>69</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B16" t="s">
@@ -6019,14 +5443,10 @@
       <c r="E16" s="1">
         <v>3252</v>
       </c>
-      <c r="F16">
-        <f t="shared" si="0"/>
-        <v>85</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B17" t="s">
@@ -6041,14 +5461,10 @@
       <c r="E17" s="1">
         <v>3460</v>
       </c>
-      <c r="F17">
-        <f t="shared" si="0"/>
-        <v>77</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B18" t="s">
@@ -6063,14 +5479,10 @@
       <c r="E18" s="1">
         <v>3670</v>
       </c>
-      <c r="F18">
-        <f t="shared" si="0"/>
-        <v>86</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="B19" t="s">
@@ -6085,14 +5497,10 @@
       <c r="E19" s="1">
         <v>3880</v>
       </c>
-      <c r="F19">
-        <f t="shared" si="0"/>
-        <v>74</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="B20" t="s">
@@ -6107,14 +5515,10 @@
       <c r="E20" s="1">
         <v>4090</v>
       </c>
-      <c r="F20">
-        <f t="shared" si="0"/>
-        <v>89</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="B21" t="s">
@@ -6128,10 +5532,6 @@
       </c>
       <c r="E21" s="1">
         <v>4300</v>
-      </c>
-      <c r="F21">
-        <f t="shared" si="0"/>
-        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -6141,7 +5541,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D2BF0A5-A8EE-604E-9491-0D3375FD8BBF}">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
@@ -6153,7 +5553,7 @@
     <col min="7" max="7" width="17.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>2</v>
       </c>
@@ -6178,11 +5578,8 @@
       <c r="H1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="4" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="8">
         <v>1</v>
       </c>
@@ -6207,12 +5604,8 @@
       <c r="H2" s="8">
         <v>815</v>
       </c>
-      <c r="I2">
-        <f>H2-G2</f>
-        <v>633</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="8">
         <v>2</v>
       </c>
@@ -6237,12 +5630,8 @@
       <c r="H3" s="8">
         <v>1601</v>
       </c>
-      <c r="I3">
-        <f>H3-G3</f>
-        <v>603</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="8">
         <v>3</v>
       </c>
@@ -6267,12 +5656,8 @@
       <c r="H4" s="8">
         <v>2417</v>
       </c>
-      <c r="I4">
-        <f>H4-G4</f>
-        <v>539</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="8">
         <v>4</v>
       </c>
@@ -6297,12 +5682,8 @@
       <c r="H5" s="8">
         <v>3183</v>
       </c>
-      <c r="I5">
-        <f>H5-G5</f>
-        <v>563</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="8">
         <v>1</v>
       </c>
@@ -6327,12 +5708,8 @@
       <c r="H6" s="8">
         <v>815</v>
       </c>
-      <c r="I6">
-        <f>H6-G6</f>
-        <v>633</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="8">
         <v>2</v>
       </c>
@@ -6357,12 +5734,8 @@
       <c r="H7" s="8">
         <v>1601</v>
       </c>
-      <c r="I7">
-        <f>H7-G7</f>
-        <v>603</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="8">
         <v>3</v>
       </c>
@@ -6387,12 +5760,8 @@
       <c r="H8" s="8">
         <v>2417</v>
       </c>
-      <c r="I8">
-        <f>H8-G8</f>
-        <v>539</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="8">
         <v>4</v>
       </c>
@@ -6417,12 +5786,8 @@
       <c r="H9" s="8">
         <v>3183</v>
       </c>
-      <c r="I9">
-        <f>H9-G9</f>
-        <v>563</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="8">
         <v>1</v>
       </c>
@@ -6447,12 +5812,8 @@
       <c r="H10" s="8">
         <v>815</v>
       </c>
-      <c r="I10">
-        <f>H10-G10</f>
-        <v>633</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="8">
         <v>2</v>
       </c>
@@ -6477,12 +5838,8 @@
       <c r="H11" s="8">
         <v>1601</v>
       </c>
-      <c r="I11">
-        <f>H11-G11</f>
-        <v>603</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="8">
         <v>3</v>
       </c>
@@ -6507,12 +5864,8 @@
       <c r="H12" s="8">
         <v>2417</v>
       </c>
-      <c r="I12">
-        <f>H12-G12</f>
-        <v>539</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="8">
         <v>4</v>
       </c>
@@ -6537,12 +5890,8 @@
       <c r="H13" s="8">
         <v>3183</v>
       </c>
-      <c r="I13">
-        <f>H13-G13</f>
-        <v>563</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="8">
         <v>1</v>
       </c>
@@ -6567,12 +5916,8 @@
       <c r="H14" s="8">
         <v>815</v>
       </c>
-      <c r="I14">
-        <f>H14-G14</f>
-        <v>633</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="8">
         <v>2</v>
       </c>
@@ -6597,12 +5942,8 @@
       <c r="H15" s="8">
         <v>1601</v>
       </c>
-      <c r="I15">
-        <f>H15-G15</f>
-        <v>603</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="8">
         <v>3</v>
       </c>
@@ -6627,12 +5968,8 @@
       <c r="H16" s="8">
         <v>2417</v>
       </c>
-      <c r="I16">
-        <f>H16-G16</f>
-        <v>539</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="8">
         <v>4</v>
       </c>
@@ -6656,10 +5993,6 @@
       </c>
       <c r="H17" s="8">
         <v>3183</v>
-      </c>
-      <c r="I17">
-        <f>H17-G17</f>
-        <v>563</v>
       </c>
     </row>
   </sheetData>
@@ -6669,7 +6002,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{439C113F-202D-B04C-996D-E55AD1706AE8}">
-  <dimension ref="A1:I114"/>
+  <dimension ref="A1:H114"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
@@ -6680,7 +6013,7 @@
     <col min="7" max="8" width="14.6640625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>2</v>
       </c>
@@ -6705,11 +6038,8 @@
       <c r="H1" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="4" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="8">
         <v>1</v>
       </c>
@@ -6736,12 +6066,8 @@
         <f>LEFT(E2,2)*3600*30 + MID(E2,4,2)*60*30 + MID(E2,7,2)*30 + RIGHT(E2,2)</f>
         <v>846</v>
       </c>
-      <c r="I2">
-        <f>H2-G2</f>
-        <v>660</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="8">
         <v>2</v>
       </c>
@@ -6768,12 +6094,8 @@
         <f t="shared" si="0"/>
         <v>1560</v>
       </c>
-      <c r="I3">
-        <f t="shared" ref="I3:I66" si="1">H3-G3</f>
-        <v>654</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="8">
         <v>3</v>
       </c>
@@ -6800,12 +6122,8 @@
         <f t="shared" si="0"/>
         <v>2273</v>
       </c>
-      <c r="I4">
-        <f t="shared" si="1"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="8">
         <v>4</v>
       </c>
@@ -6832,12 +6150,8 @@
         <f t="shared" si="0"/>
         <v>2986</v>
       </c>
-      <c r="I5">
-        <f t="shared" si="1"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="8">
         <v>5</v>
       </c>
@@ -6864,12 +6178,8 @@
         <f t="shared" si="0"/>
         <v>3700</v>
       </c>
-      <c r="I6">
-        <f t="shared" si="1"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="8">
         <v>6</v>
       </c>
@@ -6896,12 +6206,8 @@
         <f t="shared" si="0"/>
         <v>4413</v>
       </c>
-      <c r="I7">
-        <f t="shared" si="1"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="8">
         <v>7</v>
       </c>
@@ -6928,12 +6234,8 @@
         <f t="shared" si="0"/>
         <v>5373</v>
       </c>
-      <c r="I8">
-        <f t="shared" si="1"/>
-        <v>900</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="8">
         <v>8</v>
       </c>
@@ -6960,12 +6262,8 @@
         <f t="shared" si="0"/>
         <v>6117</v>
       </c>
-      <c r="I9">
-        <f t="shared" si="1"/>
-        <v>684</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="8">
         <v>9</v>
       </c>
@@ -6992,12 +6290,8 @@
         <f t="shared" si="0"/>
         <v>6830</v>
       </c>
-      <c r="I10">
-        <f t="shared" si="1"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="8">
         <v>10</v>
       </c>
@@ -7024,12 +6318,8 @@
         <f t="shared" si="0"/>
         <v>7543</v>
       </c>
-      <c r="I11">
-        <f t="shared" si="1"/>
-        <v>654</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="8">
         <v>11</v>
       </c>
@@ -7056,12 +6346,8 @@
         <f t="shared" si="0"/>
         <v>8256</v>
       </c>
-      <c r="I12">
-        <f t="shared" si="1"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="8">
         <v>12</v>
       </c>
@@ -7088,12 +6374,8 @@
         <f t="shared" si="0"/>
         <v>8969</v>
       </c>
-      <c r="I13">
-        <f t="shared" si="1"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="8">
         <v>13</v>
       </c>
@@ -7120,12 +6402,8 @@
         <f t="shared" si="0"/>
         <v>9683</v>
       </c>
-      <c r="I14">
-        <f t="shared" si="1"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="8">
         <v>14</v>
       </c>
@@ -7152,12 +6430,8 @@
         <f t="shared" si="0"/>
         <v>10642</v>
       </c>
-      <c r="I15">
-        <f t="shared" si="1"/>
-        <v>899</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="8">
         <v>1</v>
       </c>
@@ -7184,12 +6458,8 @@
         <f t="shared" si="0"/>
         <v>846</v>
       </c>
-      <c r="I16">
-        <f t="shared" si="1"/>
-        <v>660</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="8">
         <v>2</v>
       </c>
@@ -7216,12 +6486,8 @@
         <f t="shared" si="0"/>
         <v>1560</v>
       </c>
-      <c r="I17">
-        <f t="shared" si="1"/>
-        <v>654</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="8">
         <v>3</v>
       </c>
@@ -7248,12 +6514,8 @@
         <f t="shared" si="0"/>
         <v>2273</v>
       </c>
-      <c r="I18">
-        <f t="shared" si="1"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="8">
         <v>4</v>
       </c>
@@ -7280,12 +6542,8 @@
         <f t="shared" si="0"/>
         <v>2986</v>
       </c>
-      <c r="I19">
-        <f t="shared" si="1"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="8">
         <v>5</v>
       </c>
@@ -7312,12 +6570,8 @@
         <f t="shared" si="0"/>
         <v>3700</v>
       </c>
-      <c r="I20">
-        <f t="shared" si="1"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="8">
         <v>6</v>
       </c>
@@ -7344,12 +6598,8 @@
         <f t="shared" si="0"/>
         <v>4413</v>
       </c>
-      <c r="I21">
-        <f t="shared" si="1"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="8">
         <v>7</v>
       </c>
@@ -7376,12 +6626,8 @@
         <f t="shared" si="0"/>
         <v>5373</v>
       </c>
-      <c r="I22">
-        <f t="shared" si="1"/>
-        <v>900</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="8">
         <v>8</v>
       </c>
@@ -7408,12 +6654,8 @@
         <f t="shared" si="0"/>
         <v>6117</v>
       </c>
-      <c r="I23">
-        <f t="shared" si="1"/>
-        <v>684</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="8">
         <v>9</v>
       </c>
@@ -7440,12 +6682,8 @@
         <f t="shared" si="0"/>
         <v>6830</v>
       </c>
-      <c r="I24">
-        <f t="shared" si="1"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="8">
         <v>10</v>
       </c>
@@ -7472,12 +6710,8 @@
         <f t="shared" si="0"/>
         <v>7543</v>
       </c>
-      <c r="I25">
-        <f t="shared" si="1"/>
-        <v>654</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="8">
         <v>11</v>
       </c>
@@ -7504,12 +6738,8 @@
         <f t="shared" si="0"/>
         <v>8256</v>
       </c>
-      <c r="I26">
-        <f t="shared" si="1"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="8">
         <v>12</v>
       </c>
@@ -7536,12 +6766,8 @@
         <f t="shared" si="0"/>
         <v>8969</v>
       </c>
-      <c r="I27">
-        <f t="shared" si="1"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="8">
         <v>13</v>
       </c>
@@ -7568,12 +6794,8 @@
         <f t="shared" si="0"/>
         <v>9683</v>
       </c>
-      <c r="I28">
-        <f t="shared" si="1"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="8">
         <v>14</v>
       </c>
@@ -7600,12 +6822,8 @@
         <f t="shared" si="0"/>
         <v>10642</v>
       </c>
-      <c r="I29">
-        <f t="shared" si="1"/>
-        <v>899</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="8">
         <v>1</v>
       </c>
@@ -7632,12 +6850,8 @@
         <f t="shared" si="0"/>
         <v>846</v>
       </c>
-      <c r="I30">
-        <f t="shared" si="1"/>
-        <v>660</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="8">
         <v>2</v>
       </c>
@@ -7664,12 +6878,8 @@
         <f t="shared" si="0"/>
         <v>1560</v>
       </c>
-      <c r="I31">
-        <f t="shared" si="1"/>
-        <v>654</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="8">
         <v>3</v>
       </c>
@@ -7696,12 +6906,8 @@
         <f t="shared" si="0"/>
         <v>2273</v>
       </c>
-      <c r="I32">
-        <f t="shared" si="1"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="8">
         <v>4</v>
       </c>
@@ -7728,12 +6934,8 @@
         <f t="shared" si="0"/>
         <v>2986</v>
       </c>
-      <c r="I33">
-        <f t="shared" si="1"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="8">
         <v>5</v>
       </c>
@@ -7760,12 +6962,8 @@
         <f t="shared" si="0"/>
         <v>3700</v>
       </c>
-      <c r="I34">
-        <f t="shared" si="1"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="8">
         <v>6</v>
       </c>
@@ -7792,12 +6990,8 @@
         <f t="shared" si="0"/>
         <v>4413</v>
       </c>
-      <c r="I35">
-        <f t="shared" si="1"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="8">
         <v>7</v>
       </c>
@@ -7824,12 +7018,8 @@
         <f t="shared" si="0"/>
         <v>5373</v>
       </c>
-      <c r="I36">
-        <f t="shared" si="1"/>
-        <v>900</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="8">
         <v>8</v>
       </c>
@@ -7856,12 +7046,8 @@
         <f t="shared" si="0"/>
         <v>6117</v>
       </c>
-      <c r="I37">
-        <f t="shared" si="1"/>
-        <v>684</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="8">
         <v>9</v>
       </c>
@@ -7888,12 +7074,8 @@
         <f t="shared" si="0"/>
         <v>6830</v>
       </c>
-      <c r="I38">
-        <f t="shared" si="1"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="8">
         <v>10</v>
       </c>
@@ -7920,12 +7102,8 @@
         <f t="shared" si="0"/>
         <v>7543</v>
       </c>
-      <c r="I39">
-        <f t="shared" si="1"/>
-        <v>654</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="8">
         <v>11</v>
       </c>
@@ -7952,12 +7130,8 @@
         <f t="shared" si="0"/>
         <v>8256</v>
       </c>
-      <c r="I40">
-        <f t="shared" si="1"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="8">
         <v>12</v>
       </c>
@@ -7984,12 +7158,8 @@
         <f t="shared" si="0"/>
         <v>8969</v>
       </c>
-      <c r="I41">
-        <f t="shared" si="1"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="8">
         <v>13</v>
       </c>
@@ -8016,12 +7186,8 @@
         <f t="shared" si="0"/>
         <v>9683</v>
       </c>
-      <c r="I42">
-        <f t="shared" si="1"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="8">
         <v>14</v>
       </c>
@@ -8048,12 +7214,8 @@
         <f t="shared" si="0"/>
         <v>10642</v>
       </c>
-      <c r="I43">
-        <f t="shared" si="1"/>
-        <v>899</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="8">
         <v>1</v>
       </c>
@@ -8080,12 +7242,8 @@
         <f t="shared" si="0"/>
         <v>846</v>
       </c>
-      <c r="I44">
-        <f t="shared" si="1"/>
-        <v>660</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="8">
         <v>2</v>
       </c>
@@ -8112,12 +7270,8 @@
         <f t="shared" si="0"/>
         <v>1560</v>
       </c>
-      <c r="I45">
-        <f t="shared" si="1"/>
-        <v>654</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="8">
         <v>3</v>
       </c>
@@ -8144,12 +7298,8 @@
         <f t="shared" si="0"/>
         <v>2273</v>
       </c>
-      <c r="I46">
-        <f t="shared" si="1"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="8">
         <v>4</v>
       </c>
@@ -8176,12 +7326,8 @@
         <f t="shared" si="0"/>
         <v>2986</v>
       </c>
-      <c r="I47">
-        <f t="shared" si="1"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="8">
         <v>5</v>
       </c>
@@ -8208,12 +7354,8 @@
         <f t="shared" si="0"/>
         <v>3700</v>
       </c>
-      <c r="I48">
-        <f t="shared" si="1"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="8">
         <v>6</v>
       </c>
@@ -8240,12 +7382,8 @@
         <f t="shared" si="0"/>
         <v>4413</v>
       </c>
-      <c r="I49">
-        <f t="shared" si="1"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="8">
         <v>7</v>
       </c>
@@ -8272,12 +7410,8 @@
         <f t="shared" si="0"/>
         <v>5373</v>
       </c>
-      <c r="I50">
-        <f t="shared" si="1"/>
-        <v>900</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="8">
         <v>8</v>
       </c>
@@ -8304,12 +7438,8 @@
         <f t="shared" si="0"/>
         <v>6117</v>
       </c>
-      <c r="I51">
-        <f t="shared" si="1"/>
-        <v>684</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="8">
         <v>9</v>
       </c>
@@ -8336,12 +7466,8 @@
         <f t="shared" si="0"/>
         <v>6830</v>
       </c>
-      <c r="I52">
-        <f t="shared" si="1"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="8">
         <v>10</v>
       </c>
@@ -8368,12 +7494,8 @@
         <f t="shared" si="0"/>
         <v>7543</v>
       </c>
-      <c r="I53">
-        <f t="shared" si="1"/>
-        <v>654</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="8">
         <v>11</v>
       </c>
@@ -8400,12 +7522,8 @@
         <f t="shared" si="0"/>
         <v>8256</v>
       </c>
-      <c r="I54">
-        <f t="shared" si="1"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="8">
         <v>12</v>
       </c>
@@ -8432,12 +7550,8 @@
         <f t="shared" si="0"/>
         <v>8969</v>
       </c>
-      <c r="I55">
-        <f t="shared" si="1"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="8">
         <v>13</v>
       </c>
@@ -8464,12 +7578,8 @@
         <f t="shared" si="0"/>
         <v>9683</v>
       </c>
-      <c r="I56">
-        <f t="shared" si="1"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="8">
         <v>14</v>
       </c>
@@ -8496,12 +7606,8 @@
         <f t="shared" si="0"/>
         <v>10642</v>
       </c>
-      <c r="I57">
-        <f t="shared" si="1"/>
-        <v>899</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="8">
         <v>1</v>
       </c>
@@ -8528,12 +7634,8 @@
         <f t="shared" si="0"/>
         <v>846</v>
       </c>
-      <c r="I58">
-        <f t="shared" si="1"/>
-        <v>660</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="8">
         <v>2</v>
       </c>
@@ -8560,12 +7662,8 @@
         <f t="shared" si="0"/>
         <v>1560</v>
       </c>
-      <c r="I59">
-        <f t="shared" si="1"/>
-        <v>654</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="8">
         <v>3</v>
       </c>
@@ -8592,12 +7690,8 @@
         <f t="shared" si="0"/>
         <v>2273</v>
       </c>
-      <c r="I60">
-        <f t="shared" si="1"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" s="8">
         <v>4</v>
       </c>
@@ -8624,12 +7718,8 @@
         <f t="shared" si="0"/>
         <v>2986</v>
       </c>
-      <c r="I61">
-        <f t="shared" si="1"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="8">
         <v>5</v>
       </c>
@@ -8656,12 +7746,8 @@
         <f t="shared" si="0"/>
         <v>3700</v>
       </c>
-      <c r="I62">
-        <f t="shared" si="1"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="8">
         <v>6</v>
       </c>
@@ -8688,12 +7774,8 @@
         <f t="shared" si="0"/>
         <v>4413</v>
       </c>
-      <c r="I63">
-        <f t="shared" si="1"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="8">
         <v>7</v>
       </c>
@@ -8720,12 +7802,8 @@
         <f t="shared" si="0"/>
         <v>5373</v>
       </c>
-      <c r="I64">
-        <f t="shared" si="1"/>
-        <v>900</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="8">
         <v>8</v>
       </c>
@@ -8752,12 +7830,8 @@
         <f t="shared" si="0"/>
         <v>6117</v>
       </c>
-      <c r="I65">
-        <f t="shared" si="1"/>
-        <v>684</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" s="8">
         <v>9</v>
       </c>
@@ -8784,12 +7858,8 @@
         <f t="shared" si="0"/>
         <v>6830</v>
       </c>
-      <c r="I66">
-        <f t="shared" si="1"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="8">
         <v>10</v>
       </c>
@@ -8809,19 +7879,15 @@
         <v>274</v>
       </c>
       <c r="G67" s="6">
-        <f t="shared" ref="G67:H113" si="2">LEFT(D67,2)*3600*30 + MID(D67,4,2)*60*30 + MID(D67,7,2)*30 + RIGHT(D67,2)</f>
+        <f t="shared" ref="G67:H113" si="1">LEFT(D67,2)*3600*30 + MID(D67,4,2)*60*30 + MID(D67,7,2)*30 + RIGHT(D67,2)</f>
         <v>6889</v>
       </c>
       <c r="H67" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>7543</v>
       </c>
-      <c r="I67">
-        <f t="shared" ref="I67:I113" si="3">H67-G67</f>
-        <v>654</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="8">
         <v>11</v>
       </c>
@@ -8841,19 +7907,15 @@
         <v>275</v>
       </c>
       <c r="G68" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>7603</v>
       </c>
       <c r="H68" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>8256</v>
       </c>
-      <c r="I68">
-        <f t="shared" si="3"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="8">
         <v>12</v>
       </c>
@@ -8873,19 +7935,15 @@
         <v>274</v>
       </c>
       <c r="G69" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>8316</v>
       </c>
       <c r="H69" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>8969</v>
       </c>
-      <c r="I69">
-        <f t="shared" si="3"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="8">
         <v>13</v>
       </c>
@@ -8905,19 +7963,15 @@
         <v>275</v>
       </c>
       <c r="G70" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>9030</v>
       </c>
       <c r="H70" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>9683</v>
       </c>
-      <c r="I70">
-        <f t="shared" si="3"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="8">
         <v>14</v>
       </c>
@@ -8937,19 +7991,15 @@
         <v>283</v>
       </c>
       <c r="G71" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>9743</v>
       </c>
       <c r="H71" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>10642</v>
       </c>
-      <c r="I71">
-        <f t="shared" si="3"/>
-        <v>899</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="8">
         <v>1</v>
       </c>
@@ -8969,19 +8019,15 @@
         <v>274</v>
       </c>
       <c r="G72" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>186</v>
       </c>
       <c r="H72" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>846</v>
       </c>
-      <c r="I72">
-        <f t="shared" si="3"/>
-        <v>660</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" s="8">
         <v>2</v>
       </c>
@@ -9001,19 +8047,15 @@
         <v>275</v>
       </c>
       <c r="G73" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>906</v>
       </c>
       <c r="H73" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1560</v>
       </c>
-      <c r="I73">
-        <f t="shared" si="3"/>
-        <v>654</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" s="8">
         <v>3</v>
       </c>
@@ -9033,19 +8075,15 @@
         <v>274</v>
       </c>
       <c r="G74" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1620</v>
       </c>
       <c r="H74" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2273</v>
       </c>
-      <c r="I74">
-        <f t="shared" si="3"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" s="8">
         <v>4</v>
       </c>
@@ -9065,19 +8103,15 @@
         <v>275</v>
       </c>
       <c r="G75" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2333</v>
       </c>
       <c r="H75" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2986</v>
       </c>
-      <c r="I75">
-        <f t="shared" si="3"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" s="8">
         <v>5</v>
       </c>
@@ -9097,19 +8131,15 @@
         <v>274</v>
       </c>
       <c r="G76" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>3047</v>
       </c>
       <c r="H76" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>3700</v>
       </c>
-      <c r="I76">
-        <f t="shared" si="3"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" s="8">
         <v>6</v>
       </c>
@@ -9129,19 +8159,15 @@
         <v>275</v>
       </c>
       <c r="G77" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>3760</v>
       </c>
       <c r="H77" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>4413</v>
       </c>
-      <c r="I77">
-        <f t="shared" si="3"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" s="8">
         <v>7</v>
       </c>
@@ -9161,19 +8187,15 @@
         <v>284</v>
       </c>
       <c r="G78" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>4473</v>
       </c>
       <c r="H78" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>5373</v>
       </c>
-      <c r="I78">
-        <f t="shared" si="3"/>
-        <v>900</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" s="8">
         <v>8</v>
       </c>
@@ -9193,19 +8215,15 @@
         <v>274</v>
       </c>
       <c r="G79" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>5433</v>
       </c>
       <c r="H79" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>6117</v>
       </c>
-      <c r="I79">
-        <f t="shared" si="3"/>
-        <v>684</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" s="8">
         <v>9</v>
       </c>
@@ -9225,19 +8243,15 @@
         <v>275</v>
       </c>
       <c r="G80" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>6177</v>
       </c>
       <c r="H80" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>6830</v>
       </c>
-      <c r="I80">
-        <f t="shared" si="3"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" s="8">
         <v>10</v>
       </c>
@@ -9257,19 +8271,15 @@
         <v>274</v>
       </c>
       <c r="G81" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>6889</v>
       </c>
       <c r="H81" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>7543</v>
       </c>
-      <c r="I81">
-        <f t="shared" si="3"/>
-        <v>654</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" s="8">
         <v>11</v>
       </c>
@@ -9289,19 +8299,15 @@
         <v>275</v>
       </c>
       <c r="G82" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>7603</v>
       </c>
       <c r="H82" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>8256</v>
       </c>
-      <c r="I82">
-        <f t="shared" si="3"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" s="8">
         <v>12</v>
       </c>
@@ -9321,19 +8327,15 @@
         <v>274</v>
       </c>
       <c r="G83" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>8316</v>
       </c>
       <c r="H83" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>8969</v>
       </c>
-      <c r="I83">
-        <f t="shared" si="3"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" s="8">
         <v>13</v>
       </c>
@@ -9353,19 +8355,15 @@
         <v>275</v>
       </c>
       <c r="G84" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>9030</v>
       </c>
       <c r="H84" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>9683</v>
       </c>
-      <c r="I84">
-        <f t="shared" si="3"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" s="8">
         <v>14</v>
       </c>
@@ -9385,19 +8383,15 @@
         <v>280</v>
       </c>
       <c r="G85" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>9743</v>
       </c>
       <c r="H85" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>10642</v>
       </c>
-      <c r="I85">
-        <f t="shared" si="3"/>
-        <v>899</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" s="8">
         <v>1</v>
       </c>
@@ -9417,19 +8411,15 @@
         <v>275</v>
       </c>
       <c r="G86" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>186</v>
       </c>
       <c r="H86" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>846</v>
       </c>
-      <c r="I86">
-        <f t="shared" si="3"/>
-        <v>660</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" s="8">
         <v>2</v>
       </c>
@@ -9449,19 +8439,15 @@
         <v>274</v>
       </c>
       <c r="G87" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>906</v>
       </c>
       <c r="H87" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1560</v>
       </c>
-      <c r="I87">
-        <f t="shared" si="3"/>
-        <v>654</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" s="8">
         <v>3</v>
       </c>
@@ -9481,19 +8467,15 @@
         <v>275</v>
       </c>
       <c r="G88" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1620</v>
       </c>
       <c r="H88" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2273</v>
       </c>
-      <c r="I88">
-        <f t="shared" si="3"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" s="8">
         <v>4</v>
       </c>
@@ -9513,19 +8495,15 @@
         <v>274</v>
       </c>
       <c r="G89" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2333</v>
       </c>
       <c r="H89" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2986</v>
       </c>
-      <c r="I89">
-        <f t="shared" si="3"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" s="8">
         <v>5</v>
       </c>
@@ -9545,19 +8523,15 @@
         <v>275</v>
       </c>
       <c r="G90" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>3047</v>
       </c>
       <c r="H90" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>3700</v>
       </c>
-      <c r="I90">
-        <f t="shared" si="3"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" s="8">
         <v>6</v>
       </c>
@@ -9577,19 +8551,15 @@
         <v>274</v>
       </c>
       <c r="G91" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>3760</v>
       </c>
       <c r="H91" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>4413</v>
       </c>
-      <c r="I91">
-        <f t="shared" si="3"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" s="8">
         <v>7</v>
       </c>
@@ -9609,19 +8579,15 @@
         <v>285</v>
       </c>
       <c r="G92" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>4473</v>
       </c>
       <c r="H92" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>5373</v>
       </c>
-      <c r="I92">
-        <f t="shared" si="3"/>
-        <v>900</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" s="8">
         <v>8</v>
       </c>
@@ -9641,19 +8607,15 @@
         <v>275</v>
       </c>
       <c r="G93" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>5433</v>
       </c>
       <c r="H93" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>6117</v>
       </c>
-      <c r="I93">
-        <f t="shared" si="3"/>
-        <v>684</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" s="8">
         <v>9</v>
       </c>
@@ -9673,19 +8635,15 @@
         <v>274</v>
       </c>
       <c r="G94" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>6177</v>
       </c>
       <c r="H94" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>6830</v>
       </c>
-      <c r="I94">
-        <f t="shared" si="3"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" s="8">
         <v>10</v>
       </c>
@@ -9705,19 +8663,15 @@
         <v>275</v>
       </c>
       <c r="G95" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>6889</v>
       </c>
       <c r="H95" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>7543</v>
       </c>
-      <c r="I95">
-        <f t="shared" si="3"/>
-        <v>654</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" s="8">
         <v>11</v>
       </c>
@@ -9737,19 +8691,15 @@
         <v>274</v>
       </c>
       <c r="G96" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>7603</v>
       </c>
       <c r="H96" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>8256</v>
       </c>
-      <c r="I96">
-        <f t="shared" si="3"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" s="8">
         <v>12</v>
       </c>
@@ -9769,19 +8719,15 @@
         <v>275</v>
       </c>
       <c r="G97" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>8316</v>
       </c>
       <c r="H97" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>8969</v>
       </c>
-      <c r="I97">
-        <f t="shared" si="3"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98" s="8">
         <v>13</v>
       </c>
@@ -9801,19 +8747,15 @@
         <v>274</v>
       </c>
       <c r="G98" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>9030</v>
       </c>
       <c r="H98" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>9683</v>
       </c>
-      <c r="I98">
-        <f t="shared" si="3"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99" s="8">
         <v>14</v>
       </c>
@@ -9833,19 +8775,15 @@
         <v>281</v>
       </c>
       <c r="G99" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>9743</v>
       </c>
       <c r="H99" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>10642</v>
       </c>
-      <c r="I99">
-        <f t="shared" si="3"/>
-        <v>899</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100" s="8">
         <v>1</v>
       </c>
@@ -9865,19 +8803,15 @@
         <v>275</v>
       </c>
       <c r="G100" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>186</v>
       </c>
       <c r="H100" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>846</v>
       </c>
-      <c r="I100">
-        <f t="shared" si="3"/>
-        <v>660</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101" s="8">
         <v>2</v>
       </c>
@@ -9897,19 +8831,15 @@
         <v>274</v>
       </c>
       <c r="G101" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>906</v>
       </c>
       <c r="H101" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1560</v>
       </c>
-      <c r="I101">
-        <f t="shared" si="3"/>
-        <v>654</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A102" s="8">
         <v>3</v>
       </c>
@@ -9929,19 +8859,15 @@
         <v>275</v>
       </c>
       <c r="G102" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1620</v>
       </c>
       <c r="H102" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2273</v>
       </c>
-      <c r="I102">
-        <f t="shared" si="3"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103" s="8">
         <v>4</v>
       </c>
@@ -9961,19 +8887,15 @@
         <v>274</v>
       </c>
       <c r="G103" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2333</v>
       </c>
       <c r="H103" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2986</v>
       </c>
-      <c r="I103">
-        <f t="shared" si="3"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A104" s="8">
         <v>5</v>
       </c>
@@ -9993,19 +8915,15 @@
         <v>275</v>
       </c>
       <c r="G104" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>3047</v>
       </c>
       <c r="H104" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>3700</v>
       </c>
-      <c r="I104">
-        <f t="shared" si="3"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105" s="8">
         <v>6</v>
       </c>
@@ -10025,19 +8943,15 @@
         <v>274</v>
       </c>
       <c r="G105" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>3760</v>
       </c>
       <c r="H105" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>4413</v>
       </c>
-      <c r="I105">
-        <f t="shared" si="3"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A106" s="8">
         <v>7</v>
       </c>
@@ -10057,19 +8971,15 @@
         <v>284</v>
       </c>
       <c r="G106" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>4473</v>
       </c>
       <c r="H106" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>5373</v>
       </c>
-      <c r="I106">
-        <f t="shared" si="3"/>
-        <v>900</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A107" s="8">
         <v>8</v>
       </c>
@@ -10089,19 +8999,15 @@
         <v>275</v>
       </c>
       <c r="G107" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>5433</v>
       </c>
       <c r="H107" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>6117</v>
       </c>
-      <c r="I107">
-        <f t="shared" si="3"/>
-        <v>684</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A108" s="8">
         <v>9</v>
       </c>
@@ -10121,19 +9027,15 @@
         <v>274</v>
       </c>
       <c r="G108" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>6177</v>
       </c>
       <c r="H108" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>6830</v>
       </c>
-      <c r="I108">
-        <f t="shared" si="3"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A109" s="8">
         <v>10</v>
       </c>
@@ -10153,19 +9055,15 @@
         <v>275</v>
       </c>
       <c r="G109" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>6889</v>
       </c>
       <c r="H109" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>7543</v>
       </c>
-      <c r="I109">
-        <f t="shared" si="3"/>
-        <v>654</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A110" s="8">
         <v>11</v>
       </c>
@@ -10185,19 +9083,15 @@
         <v>274</v>
       </c>
       <c r="G110" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>7603</v>
       </c>
       <c r="H110" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>8256</v>
       </c>
-      <c r="I110">
-        <f t="shared" si="3"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A111" s="8">
         <v>12</v>
       </c>
@@ -10217,19 +9111,15 @@
         <v>275</v>
       </c>
       <c r="G111" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>8316</v>
       </c>
       <c r="H111" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>8969</v>
       </c>
-      <c r="I111">
-        <f t="shared" si="3"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A112" s="8">
         <v>13</v>
       </c>
@@ -10249,19 +9139,15 @@
         <v>274</v>
       </c>
       <c r="G112" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>9030</v>
       </c>
       <c r="H112" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>9683</v>
       </c>
-      <c r="I112">
-        <f t="shared" si="3"/>
-        <v>653</v>
-      </c>
-    </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A113" s="8">
         <v>14</v>
       </c>
@@ -10281,19 +9167,15 @@
         <v>280</v>
       </c>
       <c r="G113" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>9743</v>
       </c>
       <c r="H113" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>10642</v>
       </c>
-      <c r="I113">
-        <f t="shared" si="3"/>
-        <v>899</v>
-      </c>
-    </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B114"/>
     </row>
   </sheetData>
@@ -10313,15 +9195,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001AAE30F29BC98549A6C45B45271C5A83" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="70fc1eee7aebc44ac40704a4c778e204">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6c0d6bb4-bf93-46e5-af3e-76fbe0d2898f" xmlns:ns3="cb5fc986-ca15-48a6-9872-3e00e06f3290" xmlns:ns4="897aa84e-6803-47c8-b68c-17d5fde4eba2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="84c483e3029d41a0188f1887cde70bc3" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="6c0d6bb4-bf93-46e5-af3e-76fbe0d2898f"/>
@@ -10587,6 +9460,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6730D68A-F459-44B9-B55A-08A4C6EDF8D4}">
   <ds:schemaRefs>
@@ -10606,14 +9488,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0CDED83-EA4E-4F36-A05F-0665C2CE98F5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D8C1EA4-A689-4448-B5CD-185A3AA72068}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10631,4 +9505,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0CDED83-EA4E-4F36-A05F-0665C2CE98F5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>